--- a/automation/Test Results/Excel/Passed_Test_Cases.xlsx
+++ b/automation/Test Results/Excel/Passed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2535" uniqueCount="1042">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2555" uniqueCount="1050">
   <si>
     <t>Test ID</t>
   </si>
@@ -100,6 +100,12 @@
     <t>Authentication Test Scenario #9 - Validate authentication component behavior 9</t>
   </si>
   <si>
+    <t>TC_AUTH_010</t>
+  </si>
+  <si>
+    <t>Authentication Test Scenario #10 - Validate authentication component behavior 10</t>
+  </si>
+  <si>
     <t>TC_AUTH_011</t>
   </si>
   <si>
@@ -1060,6 +1066,12 @@
     <t>Forms Test Scenario #7 - Validate forms component behavior 7</t>
   </si>
   <si>
+    <t>TC_FORM_008</t>
+  </si>
+  <si>
+    <t>Forms Test Scenario #8 - Validate forms component behavior 8</t>
+  </si>
+  <si>
     <t>TC_FORM_009</t>
   </si>
   <si>
@@ -2251,6 +2263,12 @@
     <t>Notifications Test Scenario #3 - Validate notifications component behavior 3</t>
   </si>
   <si>
+    <t>TC_NOTIF_004</t>
+  </si>
+  <si>
+    <t>Notifications Test Scenario #4 - Validate notifications component behavior 4</t>
+  </si>
+  <si>
     <t>TC_NOTIF_005</t>
   </si>
   <si>
@@ -2354,6 +2372,12 @@
   </si>
   <si>
     <t>File Upload Test Scenario #1 - Validate file upload component behavior 1</t>
+  </si>
+  <si>
+    <t>TC_UPLD_002</t>
+  </si>
+  <si>
+    <t>File Upload Test Scenario #2 - Validate file upload component behavior 2</t>
   </si>
   <si>
     <t>TC_UPLD_003</t>
@@ -3523,7 +3547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E507"/>
+  <dimension ref="A1:E511"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3713,7 +3737,7 @@
         <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -3730,7 +3754,7 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -3747,7 +3771,7 @@
         <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -3764,7 +3788,7 @@
         <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -3781,7 +3805,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -3798,7 +3822,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -3815,7 +3839,7 @@
         <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -3832,7 +3856,7 @@
         <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -3849,7 +3873,7 @@
         <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -3866,7 +3890,7 @@
         <v>48</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -3883,7 +3907,7 @@
         <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -3900,7 +3924,7 @@
         <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -3917,7 +3941,7 @@
         <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -3934,7 +3958,7 @@
         <v>56</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -3951,7 +3975,7 @@
         <v>58</v>
       </c>
       <c r="D25" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -3968,7 +3992,7 @@
         <v>60</v>
       </c>
       <c r="D26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -3985,7 +4009,7 @@
         <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -4002,7 +4026,7 @@
         <v>64</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
@@ -4019,7 +4043,7 @@
         <v>66</v>
       </c>
       <c r="D29" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -4036,7 +4060,7 @@
         <v>68</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
@@ -4053,7 +4077,7 @@
         <v>70</v>
       </c>
       <c r="D31" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -4070,7 +4094,7 @@
         <v>72</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -4087,7 +4111,7 @@
         <v>74</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
@@ -4104,7 +4128,7 @@
         <v>76</v>
       </c>
       <c r="D34" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -4121,7 +4145,7 @@
         <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
@@ -4138,7 +4162,7 @@
         <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
@@ -4155,7 +4179,7 @@
         <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E37" t="s">
         <v>9</v>
@@ -4172,7 +4196,7 @@
         <v>84</v>
       </c>
       <c r="D38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
@@ -4189,7 +4213,7 @@
         <v>86</v>
       </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
@@ -4206,7 +4230,7 @@
         <v>88</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E40" t="s">
         <v>9</v>
@@ -4217,13 +4241,13 @@
         <v>89</v>
       </c>
       <c r="B41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" t="s">
         <v>90</v>
       </c>
-      <c r="C41" t="s">
-        <v>91</v>
-      </c>
       <c r="D41" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E41" t="s">
         <v>9</v>
@@ -4231,16 +4255,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" t="s">
         <v>92</v>
-      </c>
-      <c r="B42" t="s">
-        <v>90</v>
       </c>
       <c r="C42" t="s">
         <v>93</v>
       </c>
       <c r="D42" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E42" t="s">
         <v>9</v>
@@ -4251,13 +4275,13 @@
         <v>94</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C43" t="s">
         <v>95</v>
       </c>
       <c r="D43" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E43" t="s">
         <v>9</v>
@@ -4268,13 +4292,13 @@
         <v>96</v>
       </c>
       <c r="B44" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C44" t="s">
         <v>97</v>
       </c>
       <c r="D44" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E44" t="s">
         <v>9</v>
@@ -4285,13 +4309,13 @@
         <v>98</v>
       </c>
       <c r="B45" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C45" t="s">
         <v>99</v>
       </c>
       <c r="D45" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E45" t="s">
         <v>9</v>
@@ -4302,13 +4326,13 @@
         <v>100</v>
       </c>
       <c r="B46" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C46" t="s">
         <v>101</v>
       </c>
       <c r="D46" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E46" t="s">
         <v>9</v>
@@ -4319,13 +4343,13 @@
         <v>102</v>
       </c>
       <c r="B47" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C47" t="s">
         <v>103</v>
       </c>
       <c r="D47" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E47" t="s">
         <v>9</v>
@@ -4336,13 +4360,13 @@
         <v>104</v>
       </c>
       <c r="B48" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C48" t="s">
         <v>105</v>
       </c>
       <c r="D48" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E48" t="s">
         <v>9</v>
@@ -4353,13 +4377,13 @@
         <v>106</v>
       </c>
       <c r="B49" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C49" t="s">
         <v>107</v>
       </c>
       <c r="D49" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E49" t="s">
         <v>9</v>
@@ -4370,13 +4394,13 @@
         <v>108</v>
       </c>
       <c r="B50" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C50" t="s">
         <v>109</v>
       </c>
       <c r="D50" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E50" t="s">
         <v>9</v>
@@ -4387,13 +4411,13 @@
         <v>110</v>
       </c>
       <c r="B51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C51" t="s">
         <v>111</v>
       </c>
       <c r="D51" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E51" t="s">
         <v>9</v>
@@ -4404,13 +4428,13 @@
         <v>112</v>
       </c>
       <c r="B52" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C52" t="s">
         <v>113</v>
       </c>
       <c r="D52" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E52" t="s">
         <v>9</v>
@@ -4421,13 +4445,13 @@
         <v>114</v>
       </c>
       <c r="B53" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C53" t="s">
         <v>115</v>
       </c>
       <c r="D53" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E53" t="s">
         <v>9</v>
@@ -4438,13 +4462,13 @@
         <v>116</v>
       </c>
       <c r="B54" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C54" t="s">
         <v>117</v>
       </c>
       <c r="D54" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E54" t="s">
         <v>9</v>
@@ -4455,13 +4479,13 @@
         <v>118</v>
       </c>
       <c r="B55" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C55" t="s">
         <v>119</v>
       </c>
       <c r="D55" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E55" t="s">
         <v>9</v>
@@ -4472,13 +4496,13 @@
         <v>120</v>
       </c>
       <c r="B56" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C56" t="s">
         <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E56" t="s">
         <v>9</v>
@@ -4489,13 +4513,13 @@
         <v>122</v>
       </c>
       <c r="B57" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C57" t="s">
         <v>123</v>
       </c>
       <c r="D57" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E57" t="s">
         <v>9</v>
@@ -4506,13 +4530,13 @@
         <v>124</v>
       </c>
       <c r="B58" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C58" t="s">
         <v>125</v>
       </c>
       <c r="D58" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E58" t="s">
         <v>9</v>
@@ -4523,13 +4547,13 @@
         <v>126</v>
       </c>
       <c r="B59" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C59" t="s">
         <v>127</v>
       </c>
       <c r="D59" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E59" t="s">
         <v>9</v>
@@ -4540,13 +4564,13 @@
         <v>128</v>
       </c>
       <c r="B60" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C60" t="s">
         <v>129</v>
       </c>
       <c r="D60" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E60" t="s">
         <v>9</v>
@@ -4557,13 +4581,13 @@
         <v>130</v>
       </c>
       <c r="B61" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C61" t="s">
         <v>131</v>
       </c>
       <c r="D61" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E61" t="s">
         <v>9</v>
@@ -4574,13 +4598,13 @@
         <v>132</v>
       </c>
       <c r="B62" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C62" t="s">
         <v>133</v>
       </c>
       <c r="D62" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E62" t="s">
         <v>9</v>
@@ -4591,13 +4615,13 @@
         <v>134</v>
       </c>
       <c r="B63" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C63" t="s">
         <v>135</v>
       </c>
       <c r="D63" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E63" t="s">
         <v>9</v>
@@ -4608,13 +4632,13 @@
         <v>136</v>
       </c>
       <c r="B64" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C64" t="s">
         <v>137</v>
       </c>
       <c r="D64" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E64" t="s">
         <v>9</v>
@@ -4625,13 +4649,13 @@
         <v>138</v>
       </c>
       <c r="B65" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C65" t="s">
         <v>139</v>
       </c>
       <c r="D65" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E65" t="s">
         <v>9</v>
@@ -4642,13 +4666,13 @@
         <v>140</v>
       </c>
       <c r="B66" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C66" t="s">
         <v>141</v>
       </c>
       <c r="D66" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E66" t="s">
         <v>9</v>
@@ -4659,13 +4683,13 @@
         <v>142</v>
       </c>
       <c r="B67" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C67" t="s">
         <v>143</v>
       </c>
       <c r="D67" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E67" t="s">
         <v>9</v>
@@ -4676,13 +4700,13 @@
         <v>144</v>
       </c>
       <c r="B68" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C68" t="s">
         <v>145</v>
       </c>
       <c r="D68" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E68" t="s">
         <v>9</v>
@@ -4693,13 +4717,13 @@
         <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C69" t="s">
         <v>147</v>
       </c>
       <c r="D69" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E69" t="s">
         <v>9</v>
@@ -4710,13 +4734,13 @@
         <v>148</v>
       </c>
       <c r="B70" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C70" t="s">
         <v>149</v>
       </c>
       <c r="D70" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E70" t="s">
         <v>9</v>
@@ -4727,13 +4751,13 @@
         <v>150</v>
       </c>
       <c r="B71" t="s">
+        <v>92</v>
+      </c>
+      <c r="C71" t="s">
         <v>151</v>
       </c>
-      <c r="C71" t="s">
-        <v>152</v>
-      </c>
       <c r="D71" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E71" t="s">
         <v>9</v>
@@ -4741,16 +4765,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>152</v>
+      </c>
+      <c r="B72" t="s">
         <v>153</v>
-      </c>
-      <c r="B72" t="s">
-        <v>151</v>
       </c>
       <c r="C72" t="s">
         <v>154</v>
       </c>
       <c r="D72" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E72" t="s">
         <v>9</v>
@@ -4761,13 +4785,13 @@
         <v>155</v>
       </c>
       <c r="B73" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C73" t="s">
         <v>156</v>
       </c>
       <c r="D73" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E73" t="s">
         <v>9</v>
@@ -4778,13 +4802,13 @@
         <v>157</v>
       </c>
       <c r="B74" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C74" t="s">
         <v>158</v>
       </c>
       <c r="D74" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E74" t="s">
         <v>9</v>
@@ -4795,13 +4819,13 @@
         <v>159</v>
       </c>
       <c r="B75" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C75" t="s">
         <v>160</v>
       </c>
       <c r="D75" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E75" t="s">
         <v>9</v>
@@ -4812,13 +4836,13 @@
         <v>161</v>
       </c>
       <c r="B76" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C76" t="s">
         <v>162</v>
       </c>
       <c r="D76" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E76" t="s">
         <v>9</v>
@@ -4829,13 +4853,13 @@
         <v>163</v>
       </c>
       <c r="B77" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C77" t="s">
         <v>164</v>
       </c>
       <c r="D77" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E77" t="s">
         <v>9</v>
@@ -4846,13 +4870,13 @@
         <v>165</v>
       </c>
       <c r="B78" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C78" t="s">
         <v>166</v>
       </c>
       <c r="D78" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E78" t="s">
         <v>9</v>
@@ -4863,13 +4887,13 @@
         <v>167</v>
       </c>
       <c r="B79" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C79" t="s">
         <v>168</v>
       </c>
       <c r="D79" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E79" t="s">
         <v>9</v>
@@ -4880,13 +4904,13 @@
         <v>169</v>
       </c>
       <c r="B80" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C80" t="s">
         <v>170</v>
       </c>
       <c r="D80" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E80" t="s">
         <v>9</v>
@@ -4897,13 +4921,13 @@
         <v>171</v>
       </c>
       <c r="B81" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C81" t="s">
         <v>172</v>
       </c>
       <c r="D81" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E81" t="s">
         <v>9</v>
@@ -4914,13 +4938,13 @@
         <v>173</v>
       </c>
       <c r="B82" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C82" t="s">
         <v>174</v>
       </c>
       <c r="D82" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E82" t="s">
         <v>9</v>
@@ -4931,13 +4955,13 @@
         <v>175</v>
       </c>
       <c r="B83" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C83" t="s">
         <v>176</v>
       </c>
       <c r="D83" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E83" t="s">
         <v>9</v>
@@ -4948,13 +4972,13 @@
         <v>177</v>
       </c>
       <c r="B84" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C84" t="s">
         <v>178</v>
       </c>
       <c r="D84" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E84" t="s">
         <v>9</v>
@@ -4965,13 +4989,13 @@
         <v>179</v>
       </c>
       <c r="B85" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C85" t="s">
         <v>180</v>
       </c>
       <c r="D85" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E85" t="s">
         <v>9</v>
@@ -4982,13 +5006,13 @@
         <v>181</v>
       </c>
       <c r="B86" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C86" t="s">
         <v>182</v>
       </c>
       <c r="D86" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E86" t="s">
         <v>9</v>
@@ -4999,13 +5023,13 @@
         <v>183</v>
       </c>
       <c r="B87" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C87" t="s">
         <v>184</v>
       </c>
       <c r="D87" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E87" t="s">
         <v>9</v>
@@ -5016,13 +5040,13 @@
         <v>185</v>
       </c>
       <c r="B88" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C88" t="s">
         <v>186</v>
       </c>
       <c r="D88" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E88" t="s">
         <v>9</v>
@@ -5033,13 +5057,13 @@
         <v>187</v>
       </c>
       <c r="B89" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C89" t="s">
         <v>188</v>
       </c>
       <c r="D89" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E89" t="s">
         <v>9</v>
@@ -5050,13 +5074,13 @@
         <v>189</v>
       </c>
       <c r="B90" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C90" t="s">
         <v>190</v>
       </c>
       <c r="D90" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E90" t="s">
         <v>9</v>
@@ -5067,13 +5091,13 @@
         <v>191</v>
       </c>
       <c r="B91" t="s">
+        <v>153</v>
+      </c>
+      <c r="C91" t="s">
         <v>192</v>
       </c>
-      <c r="C91" t="s">
-        <v>193</v>
-      </c>
       <c r="D91" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E91" t="s">
         <v>9</v>
@@ -5081,16 +5105,16 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>193</v>
+      </c>
+      <c r="B92" t="s">
         <v>194</v>
-      </c>
-      <c r="B92" t="s">
-        <v>192</v>
       </c>
       <c r="C92" t="s">
         <v>195</v>
       </c>
       <c r="D92" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E92" t="s">
         <v>9</v>
@@ -5101,13 +5125,13 @@
         <v>196</v>
       </c>
       <c r="B93" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C93" t="s">
         <v>197</v>
       </c>
       <c r="D93" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E93" t="s">
         <v>9</v>
@@ -5118,13 +5142,13 @@
         <v>198</v>
       </c>
       <c r="B94" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C94" t="s">
         <v>199</v>
       </c>
       <c r="D94" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E94" t="s">
         <v>9</v>
@@ -5135,13 +5159,13 @@
         <v>200</v>
       </c>
       <c r="B95" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C95" t="s">
         <v>201</v>
       </c>
       <c r="D95" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E95" t="s">
         <v>9</v>
@@ -5152,13 +5176,13 @@
         <v>202</v>
       </c>
       <c r="B96" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C96" t="s">
         <v>203</v>
       </c>
       <c r="D96" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E96" t="s">
         <v>9</v>
@@ -5169,13 +5193,13 @@
         <v>204</v>
       </c>
       <c r="B97" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C97" t="s">
         <v>205</v>
       </c>
       <c r="D97" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E97" t="s">
         <v>9</v>
@@ -5186,13 +5210,13 @@
         <v>206</v>
       </c>
       <c r="B98" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C98" t="s">
         <v>207</v>
       </c>
       <c r="D98" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E98" t="s">
         <v>9</v>
@@ -5203,13 +5227,13 @@
         <v>208</v>
       </c>
       <c r="B99" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C99" t="s">
         <v>209</v>
       </c>
       <c r="D99" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E99" t="s">
         <v>9</v>
@@ -5220,13 +5244,13 @@
         <v>210</v>
       </c>
       <c r="B100" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C100" t="s">
         <v>211</v>
       </c>
       <c r="D100" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E100" t="s">
         <v>9</v>
@@ -5237,13 +5261,13 @@
         <v>212</v>
       </c>
       <c r="B101" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C101" t="s">
         <v>213</v>
       </c>
       <c r="D101" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E101" t="s">
         <v>9</v>
@@ -5254,13 +5278,13 @@
         <v>214</v>
       </c>
       <c r="B102" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C102" t="s">
         <v>215</v>
       </c>
       <c r="D102" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E102" t="s">
         <v>9</v>
@@ -5271,13 +5295,13 @@
         <v>216</v>
       </c>
       <c r="B103" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C103" t="s">
         <v>217</v>
       </c>
       <c r="D103" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E103" t="s">
         <v>9</v>
@@ -5288,13 +5312,13 @@
         <v>218</v>
       </c>
       <c r="B104" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C104" t="s">
         <v>219</v>
       </c>
       <c r="D104" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E104" t="s">
         <v>9</v>
@@ -5305,13 +5329,13 @@
         <v>220</v>
       </c>
       <c r="B105" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C105" t="s">
         <v>221</v>
       </c>
       <c r="D105" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E105" t="s">
         <v>9</v>
@@ -5322,13 +5346,13 @@
         <v>222</v>
       </c>
       <c r="B106" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C106" t="s">
         <v>223</v>
       </c>
       <c r="D106" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E106" t="s">
         <v>9</v>
@@ -5339,13 +5363,13 @@
         <v>224</v>
       </c>
       <c r="B107" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C107" t="s">
         <v>225</v>
       </c>
       <c r="D107" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E107" t="s">
         <v>9</v>
@@ -5356,13 +5380,13 @@
         <v>226</v>
       </c>
       <c r="B108" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C108" t="s">
         <v>227</v>
       </c>
       <c r="D108" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E108" t="s">
         <v>9</v>
@@ -5373,13 +5397,13 @@
         <v>228</v>
       </c>
       <c r="B109" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C109" t="s">
         <v>229</v>
       </c>
       <c r="D109" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E109" t="s">
         <v>9</v>
@@ -5390,13 +5414,13 @@
         <v>230</v>
       </c>
       <c r="B110" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C110" t="s">
         <v>231</v>
       </c>
       <c r="D110" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E110" t="s">
         <v>9</v>
@@ -5407,13 +5431,13 @@
         <v>232</v>
       </c>
       <c r="B111" t="s">
+        <v>194</v>
+      </c>
+      <c r="C111" t="s">
         <v>233</v>
       </c>
-      <c r="C111" t="s">
-        <v>234</v>
-      </c>
       <c r="D111" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E111" t="s">
         <v>9</v>
@@ -5421,16 +5445,16 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>234</v>
+      </c>
+      <c r="B112" t="s">
         <v>235</v>
-      </c>
-      <c r="B112" t="s">
-        <v>233</v>
       </c>
       <c r="C112" t="s">
         <v>236</v>
       </c>
       <c r="D112" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E112" t="s">
         <v>9</v>
@@ -5441,13 +5465,13 @@
         <v>237</v>
       </c>
       <c r="B113" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C113" t="s">
         <v>238</v>
       </c>
       <c r="D113" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E113" t="s">
         <v>9</v>
@@ -5458,13 +5482,13 @@
         <v>239</v>
       </c>
       <c r="B114" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C114" t="s">
         <v>240</v>
       </c>
       <c r="D114" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E114" t="s">
         <v>9</v>
@@ -5475,13 +5499,13 @@
         <v>241</v>
       </c>
       <c r="B115" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C115" t="s">
         <v>242</v>
       </c>
       <c r="D115" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E115" t="s">
         <v>9</v>
@@ -5492,13 +5516,13 @@
         <v>243</v>
       </c>
       <c r="B116" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C116" t="s">
         <v>244</v>
       </c>
       <c r="D116" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E116" t="s">
         <v>9</v>
@@ -5509,13 +5533,13 @@
         <v>245</v>
       </c>
       <c r="B117" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C117" t="s">
         <v>246</v>
       </c>
       <c r="D117" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E117" t="s">
         <v>9</v>
@@ -5526,13 +5550,13 @@
         <v>247</v>
       </c>
       <c r="B118" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C118" t="s">
         <v>248</v>
       </c>
       <c r="D118" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E118" t="s">
         <v>9</v>
@@ -5543,13 +5567,13 @@
         <v>249</v>
       </c>
       <c r="B119" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C119" t="s">
         <v>250</v>
       </c>
       <c r="D119" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E119" t="s">
         <v>9</v>
@@ -5560,13 +5584,13 @@
         <v>251</v>
       </c>
       <c r="B120" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C120" t="s">
         <v>252</v>
       </c>
       <c r="D120" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E120" t="s">
         <v>9</v>
@@ -5577,13 +5601,13 @@
         <v>253</v>
       </c>
       <c r="B121" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C121" t="s">
         <v>254</v>
       </c>
       <c r="D121" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E121" t="s">
         <v>9</v>
@@ -5594,13 +5618,13 @@
         <v>255</v>
       </c>
       <c r="B122" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C122" t="s">
         <v>256</v>
       </c>
       <c r="D122" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E122" t="s">
         <v>9</v>
@@ -5611,13 +5635,13 @@
         <v>257</v>
       </c>
       <c r="B123" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C123" t="s">
         <v>258</v>
       </c>
       <c r="D123" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E123" t="s">
         <v>9</v>
@@ -5628,13 +5652,13 @@
         <v>259</v>
       </c>
       <c r="B124" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C124" t="s">
         <v>260</v>
       </c>
       <c r="D124" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E124" t="s">
         <v>9</v>
@@ -5645,13 +5669,13 @@
         <v>261</v>
       </c>
       <c r="B125" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C125" t="s">
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E125" t="s">
         <v>9</v>
@@ -5662,13 +5686,13 @@
         <v>263</v>
       </c>
       <c r="B126" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C126" t="s">
         <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E126" t="s">
         <v>9</v>
@@ -5679,13 +5703,13 @@
         <v>265</v>
       </c>
       <c r="B127" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C127" t="s">
         <v>266</v>
       </c>
       <c r="D127" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E127" t="s">
         <v>9</v>
@@ -5696,13 +5720,13 @@
         <v>267</v>
       </c>
       <c r="B128" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C128" t="s">
         <v>268</v>
       </c>
       <c r="D128" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E128" t="s">
         <v>9</v>
@@ -5713,13 +5737,13 @@
         <v>269</v>
       </c>
       <c r="B129" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C129" t="s">
         <v>270</v>
       </c>
       <c r="D129" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E129" t="s">
         <v>9</v>
@@ -5730,13 +5754,13 @@
         <v>271</v>
       </c>
       <c r="B130" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C130" t="s">
         <v>272</v>
       </c>
       <c r="D130" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E130" t="s">
         <v>9</v>
@@ -5747,13 +5771,13 @@
         <v>273</v>
       </c>
       <c r="B131" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C131" t="s">
         <v>274</v>
       </c>
       <c r="D131" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E131" t="s">
         <v>9</v>
@@ -5764,13 +5788,13 @@
         <v>275</v>
       </c>
       <c r="B132" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C132" t="s">
         <v>276</v>
       </c>
       <c r="D132" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E132" t="s">
         <v>9</v>
@@ -5781,13 +5805,13 @@
         <v>277</v>
       </c>
       <c r="B133" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C133" t="s">
         <v>278</v>
       </c>
       <c r="D133" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E133" t="s">
         <v>9</v>
@@ -5798,13 +5822,13 @@
         <v>279</v>
       </c>
       <c r="B134" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C134" t="s">
         <v>280</v>
       </c>
       <c r="D134" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E134" t="s">
         <v>9</v>
@@ -5815,13 +5839,13 @@
         <v>281</v>
       </c>
       <c r="B135" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C135" t="s">
         <v>282</v>
       </c>
       <c r="D135" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E135" t="s">
         <v>9</v>
@@ -5832,13 +5856,13 @@
         <v>283</v>
       </c>
       <c r="B136" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C136" t="s">
         <v>284</v>
       </c>
       <c r="D136" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E136" t="s">
         <v>9</v>
@@ -5849,13 +5873,13 @@
         <v>285</v>
       </c>
       <c r="B137" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C137" t="s">
         <v>286</v>
       </c>
       <c r="D137" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E137" t="s">
         <v>9</v>
@@ -5866,13 +5890,13 @@
         <v>287</v>
       </c>
       <c r="B138" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C138" t="s">
         <v>288</v>
       </c>
       <c r="D138" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E138" t="s">
         <v>9</v>
@@ -5883,13 +5907,13 @@
         <v>289</v>
       </c>
       <c r="B139" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C139" t="s">
         <v>290</v>
       </c>
       <c r="D139" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E139" t="s">
         <v>9</v>
@@ -5900,13 +5924,13 @@
         <v>291</v>
       </c>
       <c r="B140" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C140" t="s">
         <v>292</v>
       </c>
       <c r="D140" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E140" t="s">
         <v>9</v>
@@ -5917,13 +5941,13 @@
         <v>293</v>
       </c>
       <c r="B141" t="s">
+        <v>235</v>
+      </c>
+      <c r="C141" t="s">
         <v>294</v>
       </c>
-      <c r="C141" t="s">
-        <v>295</v>
-      </c>
       <c r="D141" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E141" t="s">
         <v>9</v>
@@ -5931,16 +5955,16 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>295</v>
+      </c>
+      <c r="B142" t="s">
         <v>296</v>
-      </c>
-      <c r="B142" t="s">
-        <v>294</v>
       </c>
       <c r="C142" t="s">
         <v>297</v>
       </c>
       <c r="D142" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E142" t="s">
         <v>9</v>
@@ -5951,13 +5975,13 @@
         <v>298</v>
       </c>
       <c r="B143" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C143" t="s">
         <v>299</v>
       </c>
       <c r="D143" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E143" t="s">
         <v>9</v>
@@ -5968,13 +5992,13 @@
         <v>300</v>
       </c>
       <c r="B144" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C144" t="s">
         <v>301</v>
       </c>
       <c r="D144" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E144" t="s">
         <v>9</v>
@@ -5985,13 +6009,13 @@
         <v>302</v>
       </c>
       <c r="B145" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C145" t="s">
         <v>303</v>
       </c>
       <c r="D145" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E145" t="s">
         <v>9</v>
@@ -6002,13 +6026,13 @@
         <v>304</v>
       </c>
       <c r="B146" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C146" t="s">
         <v>305</v>
       </c>
       <c r="D146" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E146" t="s">
         <v>9</v>
@@ -6019,13 +6043,13 @@
         <v>306</v>
       </c>
       <c r="B147" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C147" t="s">
         <v>307</v>
       </c>
       <c r="D147" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E147" t="s">
         <v>9</v>
@@ -6036,13 +6060,13 @@
         <v>308</v>
       </c>
       <c r="B148" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C148" t="s">
         <v>309</v>
       </c>
       <c r="D148" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E148" t="s">
         <v>9</v>
@@ -6053,13 +6077,13 @@
         <v>310</v>
       </c>
       <c r="B149" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C149" t="s">
         <v>311</v>
       </c>
       <c r="D149" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E149" t="s">
         <v>9</v>
@@ -6070,13 +6094,13 @@
         <v>312</v>
       </c>
       <c r="B150" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C150" t="s">
         <v>313</v>
       </c>
       <c r="D150" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E150" t="s">
         <v>9</v>
@@ -6087,13 +6111,13 @@
         <v>314</v>
       </c>
       <c r="B151" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C151" t="s">
         <v>315</v>
       </c>
       <c r="D151" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E151" t="s">
         <v>9</v>
@@ -6104,13 +6128,13 @@
         <v>316</v>
       </c>
       <c r="B152" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C152" t="s">
         <v>317</v>
       </c>
       <c r="D152" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E152" t="s">
         <v>9</v>
@@ -6121,13 +6145,13 @@
         <v>318</v>
       </c>
       <c r="B153" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C153" t="s">
         <v>319</v>
       </c>
       <c r="D153" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E153" t="s">
         <v>9</v>
@@ -6138,13 +6162,13 @@
         <v>320</v>
       </c>
       <c r="B154" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C154" t="s">
         <v>321</v>
       </c>
       <c r="D154" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E154" t="s">
         <v>9</v>
@@ -6155,13 +6179,13 @@
         <v>322</v>
       </c>
       <c r="B155" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C155" t="s">
         <v>323</v>
       </c>
       <c r="D155" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E155" t="s">
         <v>9</v>
@@ -6172,13 +6196,13 @@
         <v>324</v>
       </c>
       <c r="B156" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C156" t="s">
         <v>325</v>
       </c>
       <c r="D156" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E156" t="s">
         <v>9</v>
@@ -6189,13 +6213,13 @@
         <v>326</v>
       </c>
       <c r="B157" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C157" t="s">
         <v>327</v>
       </c>
       <c r="D157" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E157" t="s">
         <v>9</v>
@@ -6206,13 +6230,13 @@
         <v>328</v>
       </c>
       <c r="B158" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C158" t="s">
         <v>329</v>
       </c>
       <c r="D158" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E158" t="s">
         <v>9</v>
@@ -6223,13 +6247,13 @@
         <v>330</v>
       </c>
       <c r="B159" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C159" t="s">
         <v>331</v>
       </c>
       <c r="D159" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E159" t="s">
         <v>9</v>
@@ -6240,13 +6264,13 @@
         <v>332</v>
       </c>
       <c r="B160" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C160" t="s">
         <v>333</v>
       </c>
       <c r="D160" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E160" t="s">
         <v>9</v>
@@ -6257,13 +6281,13 @@
         <v>334</v>
       </c>
       <c r="B161" t="s">
+        <v>296</v>
+      </c>
+      <c r="C161" t="s">
         <v>335</v>
       </c>
-      <c r="C161" t="s">
-        <v>336</v>
-      </c>
       <c r="D161" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E161" t="s">
         <v>9</v>
@@ -6271,16 +6295,16 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>336</v>
+      </c>
+      <c r="B162" t="s">
         <v>337</v>
-      </c>
-      <c r="B162" t="s">
-        <v>335</v>
       </c>
       <c r="C162" t="s">
         <v>338</v>
       </c>
       <c r="D162" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E162" t="s">
         <v>9</v>
@@ -6291,13 +6315,13 @@
         <v>339</v>
       </c>
       <c r="B163" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C163" t="s">
         <v>340</v>
       </c>
       <c r="D163" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E163" t="s">
         <v>9</v>
@@ -6308,13 +6332,13 @@
         <v>341</v>
       </c>
       <c r="B164" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C164" t="s">
         <v>342</v>
       </c>
       <c r="D164" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E164" t="s">
         <v>9</v>
@@ -6325,13 +6349,13 @@
         <v>343</v>
       </c>
       <c r="B165" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C165" t="s">
         <v>344</v>
       </c>
       <c r="D165" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E165" t="s">
         <v>9</v>
@@ -6342,13 +6366,13 @@
         <v>345</v>
       </c>
       <c r="B166" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C166" t="s">
         <v>346</v>
       </c>
       <c r="D166" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E166" t="s">
         <v>9</v>
@@ -6359,13 +6383,13 @@
         <v>347</v>
       </c>
       <c r="B167" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C167" t="s">
         <v>348</v>
       </c>
       <c r="D167" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E167" t="s">
         <v>9</v>
@@ -6376,13 +6400,13 @@
         <v>349</v>
       </c>
       <c r="B168" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C168" t="s">
         <v>350</v>
       </c>
       <c r="D168" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E168" t="s">
         <v>9</v>
@@ -6393,13 +6417,13 @@
         <v>351</v>
       </c>
       <c r="B169" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C169" t="s">
         <v>352</v>
       </c>
       <c r="D169" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E169" t="s">
         <v>9</v>
@@ -6410,13 +6434,13 @@
         <v>353</v>
       </c>
       <c r="B170" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C170" t="s">
         <v>354</v>
       </c>
       <c r="D170" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E170" t="s">
         <v>9</v>
@@ -6427,13 +6451,13 @@
         <v>355</v>
       </c>
       <c r="B171" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C171" t="s">
         <v>356</v>
       </c>
       <c r="D171" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E171" t="s">
         <v>9</v>
@@ -6444,7 +6468,7 @@
         <v>357</v>
       </c>
       <c r="B172" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C172" t="s">
         <v>358</v>
@@ -6461,13 +6485,13 @@
         <v>359</v>
       </c>
       <c r="B173" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C173" t="s">
         <v>360</v>
       </c>
       <c r="D173" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E173" t="s">
         <v>9</v>
@@ -6478,13 +6502,13 @@
         <v>361</v>
       </c>
       <c r="B174" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C174" t="s">
         <v>362</v>
       </c>
       <c r="D174" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E174" t="s">
         <v>9</v>
@@ -6495,13 +6519,13 @@
         <v>363</v>
       </c>
       <c r="B175" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C175" t="s">
         <v>364</v>
       </c>
       <c r="D175" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E175" t="s">
         <v>9</v>
@@ -6512,13 +6536,13 @@
         <v>365</v>
       </c>
       <c r="B176" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C176" t="s">
         <v>366</v>
       </c>
       <c r="D176" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E176" t="s">
         <v>9</v>
@@ -6529,13 +6553,13 @@
         <v>367</v>
       </c>
       <c r="B177" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C177" t="s">
         <v>368</v>
       </c>
       <c r="D177" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E177" t="s">
         <v>9</v>
@@ -6546,7 +6570,7 @@
         <v>369</v>
       </c>
       <c r="B178" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C178" t="s">
         <v>370</v>
@@ -6563,13 +6587,13 @@
         <v>371</v>
       </c>
       <c r="B179" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C179" t="s">
         <v>372</v>
       </c>
       <c r="D179" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E179" t="s">
         <v>9</v>
@@ -6580,13 +6604,13 @@
         <v>373</v>
       </c>
       <c r="B180" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C180" t="s">
         <v>374</v>
       </c>
       <c r="D180" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E180" t="s">
         <v>9</v>
@@ -6597,13 +6621,13 @@
         <v>375</v>
       </c>
       <c r="B181" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C181" t="s">
         <v>376</v>
       </c>
       <c r="D181" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E181" t="s">
         <v>9</v>
@@ -6614,13 +6638,13 @@
         <v>377</v>
       </c>
       <c r="B182" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C182" t="s">
         <v>378</v>
       </c>
       <c r="D182" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E182" t="s">
         <v>9</v>
@@ -6631,13 +6655,13 @@
         <v>379</v>
       </c>
       <c r="B183" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C183" t="s">
         <v>380</v>
       </c>
       <c r="D183" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E183" t="s">
         <v>9</v>
@@ -6648,7 +6672,7 @@
         <v>381</v>
       </c>
       <c r="B184" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C184" t="s">
         <v>382</v>
@@ -6665,13 +6689,13 @@
         <v>383</v>
       </c>
       <c r="B185" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C185" t="s">
         <v>384</v>
       </c>
       <c r="D185" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E185" t="s">
         <v>9</v>
@@ -6682,13 +6706,13 @@
         <v>385</v>
       </c>
       <c r="B186" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C186" t="s">
         <v>386</v>
       </c>
       <c r="D186" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E186" t="s">
         <v>9</v>
@@ -6699,13 +6723,13 @@
         <v>387</v>
       </c>
       <c r="B187" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C187" t="s">
         <v>388</v>
       </c>
       <c r="D187" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E187" t="s">
         <v>9</v>
@@ -6716,13 +6740,13 @@
         <v>389</v>
       </c>
       <c r="B188" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C188" t="s">
         <v>390</v>
       </c>
       <c r="D188" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E188" t="s">
         <v>9</v>
@@ -6733,13 +6757,13 @@
         <v>391</v>
       </c>
       <c r="B189" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C189" t="s">
         <v>392</v>
       </c>
       <c r="D189" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E189" t="s">
         <v>9</v>
@@ -6750,7 +6774,7 @@
         <v>393</v>
       </c>
       <c r="B190" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C190" t="s">
         <v>394</v>
@@ -6767,13 +6791,13 @@
         <v>395</v>
       </c>
       <c r="B191" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C191" t="s">
         <v>396</v>
       </c>
       <c r="D191" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E191" t="s">
         <v>9</v>
@@ -6784,13 +6808,13 @@
         <v>397</v>
       </c>
       <c r="B192" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C192" t="s">
         <v>398</v>
       </c>
       <c r="D192" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E192" t="s">
         <v>9</v>
@@ -6801,13 +6825,13 @@
         <v>399</v>
       </c>
       <c r="B193" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C193" t="s">
         <v>400</v>
       </c>
       <c r="D193" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E193" t="s">
         <v>9</v>
@@ -6818,13 +6842,13 @@
         <v>401</v>
       </c>
       <c r="B194" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C194" t="s">
         <v>402</v>
       </c>
       <c r="D194" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E194" t="s">
         <v>9</v>
@@ -6835,13 +6859,13 @@
         <v>403</v>
       </c>
       <c r="B195" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C195" t="s">
         <v>404</v>
       </c>
       <c r="D195" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E195" t="s">
         <v>9</v>
@@ -6852,7 +6876,7 @@
         <v>405</v>
       </c>
       <c r="B196" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C196" t="s">
         <v>406</v>
@@ -6869,13 +6893,13 @@
         <v>407</v>
       </c>
       <c r="B197" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C197" t="s">
         <v>408</v>
       </c>
       <c r="D197" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E197" t="s">
         <v>9</v>
@@ -6886,13 +6910,13 @@
         <v>409</v>
       </c>
       <c r="B198" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C198" t="s">
         <v>410</v>
       </c>
       <c r="D198" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E198" t="s">
         <v>9</v>
@@ -6903,13 +6927,13 @@
         <v>411</v>
       </c>
       <c r="B199" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C199" t="s">
         <v>412</v>
       </c>
       <c r="D199" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E199" t="s">
         <v>9</v>
@@ -6920,13 +6944,13 @@
         <v>413</v>
       </c>
       <c r="B200" t="s">
+        <v>337</v>
+      </c>
+      <c r="C200" t="s">
         <v>414</v>
       </c>
-      <c r="C200" t="s">
-        <v>415</v>
-      </c>
       <c r="D200" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E200" t="s">
         <v>9</v>
@@ -6934,16 +6958,16 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
+        <v>415</v>
+      </c>
+      <c r="B201" t="s">
+        <v>337</v>
+      </c>
+      <c r="C201" t="s">
         <v>416</v>
       </c>
-      <c r="B201" t="s">
-        <v>414</v>
-      </c>
-      <c r="C201" t="s">
-        <v>417</v>
-      </c>
       <c r="D201" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E201" t="s">
         <v>9</v>
@@ -6951,16 +6975,16 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
+        <v>417</v>
+      </c>
+      <c r="B202" t="s">
         <v>418</v>
-      </c>
-      <c r="B202" t="s">
-        <v>414</v>
       </c>
       <c r="C202" t="s">
         <v>419</v>
       </c>
       <c r="D202" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E202" t="s">
         <v>9</v>
@@ -6971,13 +6995,13 @@
         <v>420</v>
       </c>
       <c r="B203" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C203" t="s">
         <v>421</v>
       </c>
       <c r="D203" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E203" t="s">
         <v>9</v>
@@ -6988,13 +7012,13 @@
         <v>422</v>
       </c>
       <c r="B204" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C204" t="s">
         <v>423</v>
       </c>
       <c r="D204" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E204" t="s">
         <v>9</v>
@@ -7005,13 +7029,13 @@
         <v>424</v>
       </c>
       <c r="B205" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C205" t="s">
         <v>425</v>
       </c>
       <c r="D205" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E205" t="s">
         <v>9</v>
@@ -7022,7 +7046,7 @@
         <v>426</v>
       </c>
       <c r="B206" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C206" t="s">
         <v>427</v>
@@ -7039,13 +7063,13 @@
         <v>428</v>
       </c>
       <c r="B207" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C207" t="s">
         <v>429</v>
       </c>
       <c r="D207" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E207" t="s">
         <v>9</v>
@@ -7056,13 +7080,13 @@
         <v>430</v>
       </c>
       <c r="B208" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C208" t="s">
         <v>431</v>
       </c>
       <c r="D208" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E208" t="s">
         <v>9</v>
@@ -7073,13 +7097,13 @@
         <v>432</v>
       </c>
       <c r="B209" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C209" t="s">
         <v>433</v>
       </c>
       <c r="D209" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E209" t="s">
         <v>9</v>
@@ -7090,13 +7114,13 @@
         <v>434</v>
       </c>
       <c r="B210" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C210" t="s">
         <v>435</v>
       </c>
       <c r="D210" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E210" t="s">
         <v>9</v>
@@ -7107,13 +7131,13 @@
         <v>436</v>
       </c>
       <c r="B211" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C211" t="s">
         <v>437</v>
       </c>
       <c r="D211" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E211" t="s">
         <v>9</v>
@@ -7124,7 +7148,7 @@
         <v>438</v>
       </c>
       <c r="B212" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C212" t="s">
         <v>439</v>
@@ -7141,13 +7165,13 @@
         <v>440</v>
       </c>
       <c r="B213" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C213" t="s">
         <v>441</v>
       </c>
       <c r="D213" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E213" t="s">
         <v>9</v>
@@ -7158,13 +7182,13 @@
         <v>442</v>
       </c>
       <c r="B214" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C214" t="s">
         <v>443</v>
       </c>
       <c r="D214" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E214" t="s">
         <v>9</v>
@@ -7175,13 +7199,13 @@
         <v>444</v>
       </c>
       <c r="B215" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C215" t="s">
         <v>445</v>
       </c>
       <c r="D215" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E215" t="s">
         <v>9</v>
@@ -7192,13 +7216,13 @@
         <v>446</v>
       </c>
       <c r="B216" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C216" t="s">
         <v>447</v>
       </c>
       <c r="D216" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E216" t="s">
         <v>9</v>
@@ -7209,13 +7233,13 @@
         <v>448</v>
       </c>
       <c r="B217" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C217" t="s">
         <v>449</v>
       </c>
       <c r="D217" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E217" t="s">
         <v>9</v>
@@ -7226,7 +7250,7 @@
         <v>450</v>
       </c>
       <c r="B218" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C218" t="s">
         <v>451</v>
@@ -7243,13 +7267,13 @@
         <v>452</v>
       </c>
       <c r="B219" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C219" t="s">
         <v>453</v>
       </c>
       <c r="D219" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E219" t="s">
         <v>9</v>
@@ -7260,13 +7284,13 @@
         <v>454</v>
       </c>
       <c r="B220" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C220" t="s">
         <v>455</v>
       </c>
       <c r="D220" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E220" t="s">
         <v>9</v>
@@ -7277,13 +7301,13 @@
         <v>456</v>
       </c>
       <c r="B221" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C221" t="s">
         <v>457</v>
       </c>
       <c r="D221" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E221" t="s">
         <v>9</v>
@@ -7294,13 +7318,13 @@
         <v>458</v>
       </c>
       <c r="B222" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C222" t="s">
         <v>459</v>
       </c>
       <c r="D222" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E222" t="s">
         <v>9</v>
@@ -7311,13 +7335,13 @@
         <v>460</v>
       </c>
       <c r="B223" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C223" t="s">
         <v>461</v>
       </c>
       <c r="D223" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E223" t="s">
         <v>9</v>
@@ -7328,7 +7352,7 @@
         <v>462</v>
       </c>
       <c r="B224" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C224" t="s">
         <v>463</v>
@@ -7345,13 +7369,13 @@
         <v>464</v>
       </c>
       <c r="B225" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C225" t="s">
         <v>465</v>
       </c>
       <c r="D225" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E225" t="s">
         <v>9</v>
@@ -7362,13 +7386,13 @@
         <v>466</v>
       </c>
       <c r="B226" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C226" t="s">
         <v>467</v>
       </c>
       <c r="D226" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E226" t="s">
         <v>9</v>
@@ -7379,13 +7403,13 @@
         <v>468</v>
       </c>
       <c r="B227" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C227" t="s">
         <v>469</v>
       </c>
       <c r="D227" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E227" t="s">
         <v>9</v>
@@ -7396,13 +7420,13 @@
         <v>470</v>
       </c>
       <c r="B228" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C228" t="s">
         <v>471</v>
       </c>
       <c r="D228" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E228" t="s">
         <v>9</v>
@@ -7413,13 +7437,13 @@
         <v>472</v>
       </c>
       <c r="B229" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C229" t="s">
         <v>473</v>
       </c>
       <c r="D229" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E229" t="s">
         <v>9</v>
@@ -7430,7 +7454,7 @@
         <v>474</v>
       </c>
       <c r="B230" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C230" t="s">
         <v>475</v>
@@ -7447,13 +7471,13 @@
         <v>476</v>
       </c>
       <c r="B231" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C231" t="s">
         <v>477</v>
       </c>
       <c r="D231" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E231" t="s">
         <v>9</v>
@@ -7464,13 +7488,13 @@
         <v>478</v>
       </c>
       <c r="B232" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C232" t="s">
         <v>479</v>
       </c>
       <c r="D232" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E232" t="s">
         <v>9</v>
@@ -7481,13 +7505,13 @@
         <v>480</v>
       </c>
       <c r="B233" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C233" t="s">
         <v>481</v>
       </c>
       <c r="D233" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E233" t="s">
         <v>9</v>
@@ -7498,13 +7522,13 @@
         <v>482</v>
       </c>
       <c r="B234" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C234" t="s">
         <v>483</v>
       </c>
       <c r="D234" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E234" t="s">
         <v>9</v>
@@ -7515,13 +7539,13 @@
         <v>484</v>
       </c>
       <c r="B235" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C235" t="s">
         <v>485</v>
       </c>
       <c r="D235" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E235" t="s">
         <v>9</v>
@@ -7532,7 +7556,7 @@
         <v>486</v>
       </c>
       <c r="B236" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C236" t="s">
         <v>487</v>
@@ -7549,13 +7573,13 @@
         <v>488</v>
       </c>
       <c r="B237" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C237" t="s">
         <v>489</v>
       </c>
       <c r="D237" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E237" t="s">
         <v>9</v>
@@ -7566,13 +7590,13 @@
         <v>490</v>
       </c>
       <c r="B238" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C238" t="s">
         <v>491</v>
       </c>
       <c r="D238" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E238" t="s">
         <v>9</v>
@@ -7583,13 +7607,13 @@
         <v>492</v>
       </c>
       <c r="B239" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C239" t="s">
         <v>493</v>
       </c>
       <c r="D239" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E239" t="s">
         <v>9</v>
@@ -7600,13 +7624,13 @@
         <v>494</v>
       </c>
       <c r="B240" t="s">
+        <v>418</v>
+      </c>
+      <c r="C240" t="s">
         <v>495</v>
       </c>
-      <c r="C240" t="s">
-        <v>496</v>
-      </c>
       <c r="D240" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E240" t="s">
         <v>9</v>
@@ -7614,16 +7638,16 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
+        <v>496</v>
+      </c>
+      <c r="B241" t="s">
+        <v>418</v>
+      </c>
+      <c r="C241" t="s">
         <v>497</v>
       </c>
-      <c r="B241" t="s">
-        <v>495</v>
-      </c>
-      <c r="C241" t="s">
-        <v>498</v>
-      </c>
       <c r="D241" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E241" t="s">
         <v>9</v>
@@ -7631,16 +7655,16 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
+        <v>498</v>
+      </c>
+      <c r="B242" t="s">
         <v>499</v>
-      </c>
-      <c r="B242" t="s">
-        <v>495</v>
       </c>
       <c r="C242" t="s">
         <v>500</v>
       </c>
       <c r="D242" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E242" t="s">
         <v>9</v>
@@ -7651,13 +7675,13 @@
         <v>501</v>
       </c>
       <c r="B243" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C243" t="s">
         <v>502</v>
       </c>
       <c r="D243" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E243" t="s">
         <v>9</v>
@@ -7668,13 +7692,13 @@
         <v>503</v>
       </c>
       <c r="B244" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C244" t="s">
         <v>504</v>
       </c>
       <c r="D244" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E244" t="s">
         <v>9</v>
@@ -7685,13 +7709,13 @@
         <v>505</v>
       </c>
       <c r="B245" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C245" t="s">
         <v>506</v>
       </c>
       <c r="D245" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E245" t="s">
         <v>9</v>
@@ -7702,7 +7726,7 @@
         <v>507</v>
       </c>
       <c r="B246" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C246" t="s">
         <v>508</v>
@@ -7719,13 +7743,13 @@
         <v>509</v>
       </c>
       <c r="B247" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C247" t="s">
         <v>510</v>
       </c>
       <c r="D247" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E247" t="s">
         <v>9</v>
@@ -7736,13 +7760,13 @@
         <v>511</v>
       </c>
       <c r="B248" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C248" t="s">
         <v>512</v>
       </c>
       <c r="D248" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E248" t="s">
         <v>9</v>
@@ -7753,13 +7777,13 @@
         <v>513</v>
       </c>
       <c r="B249" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C249" t="s">
         <v>514</v>
       </c>
       <c r="D249" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E249" t="s">
         <v>9</v>
@@ -7770,13 +7794,13 @@
         <v>515</v>
       </c>
       <c r="B250" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C250" t="s">
         <v>516</v>
       </c>
       <c r="D250" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E250" t="s">
         <v>9</v>
@@ -7787,13 +7811,13 @@
         <v>517</v>
       </c>
       <c r="B251" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C251" t="s">
         <v>518</v>
       </c>
       <c r="D251" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E251" t="s">
         <v>9</v>
@@ -7804,7 +7828,7 @@
         <v>519</v>
       </c>
       <c r="B252" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C252" t="s">
         <v>520</v>
@@ -7821,13 +7845,13 @@
         <v>521</v>
       </c>
       <c r="B253" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C253" t="s">
         <v>522</v>
       </c>
       <c r="D253" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E253" t="s">
         <v>9</v>
@@ -7838,13 +7862,13 @@
         <v>523</v>
       </c>
       <c r="B254" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C254" t="s">
         <v>524</v>
       </c>
       <c r="D254" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E254" t="s">
         <v>9</v>
@@ -7855,13 +7879,13 @@
         <v>525</v>
       </c>
       <c r="B255" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C255" t="s">
         <v>526</v>
       </c>
       <c r="D255" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E255" t="s">
         <v>9</v>
@@ -7872,13 +7896,13 @@
         <v>527</v>
       </c>
       <c r="B256" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C256" t="s">
         <v>528</v>
       </c>
       <c r="D256" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E256" t="s">
         <v>9</v>
@@ -7889,13 +7913,13 @@
         <v>529</v>
       </c>
       <c r="B257" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C257" t="s">
         <v>530</v>
       </c>
       <c r="D257" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E257" t="s">
         <v>9</v>
@@ -7906,7 +7930,7 @@
         <v>531</v>
       </c>
       <c r="B258" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C258" t="s">
         <v>532</v>
@@ -7923,13 +7947,13 @@
         <v>533</v>
       </c>
       <c r="B259" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C259" t="s">
         <v>534</v>
       </c>
       <c r="D259" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E259" t="s">
         <v>9</v>
@@ -7940,10 +7964,10 @@
         <v>535</v>
       </c>
       <c r="B260" t="s">
+        <v>499</v>
+      </c>
+      <c r="C260" t="s">
         <v>536</v>
-      </c>
-      <c r="C260" t="s">
-        <v>537</v>
       </c>
       <c r="D260" t="s">
         <v>8</v>
@@ -7954,16 +7978,16 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
+        <v>537</v>
+      </c>
+      <c r="B261" t="s">
+        <v>499</v>
+      </c>
+      <c r="C261" t="s">
         <v>538</v>
       </c>
-      <c r="B261" t="s">
-        <v>536</v>
-      </c>
-      <c r="C261" t="s">
-        <v>539</v>
-      </c>
       <c r="D261" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E261" t="s">
         <v>9</v>
@@ -7971,16 +7995,16 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
+        <v>539</v>
+      </c>
+      <c r="B262" t="s">
         <v>540</v>
-      </c>
-      <c r="B262" t="s">
-        <v>536</v>
       </c>
       <c r="C262" t="s">
         <v>541</v>
       </c>
       <c r="D262" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E262" t="s">
         <v>9</v>
@@ -7991,13 +8015,13 @@
         <v>542</v>
       </c>
       <c r="B263" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C263" t="s">
         <v>543</v>
       </c>
       <c r="D263" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E263" t="s">
         <v>9</v>
@@ -8008,13 +8032,13 @@
         <v>544</v>
       </c>
       <c r="B264" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C264" t="s">
         <v>545</v>
       </c>
       <c r="D264" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E264" t="s">
         <v>9</v>
@@ -8025,13 +8049,13 @@
         <v>546</v>
       </c>
       <c r="B265" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C265" t="s">
         <v>547</v>
       </c>
       <c r="D265" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E265" t="s">
         <v>9</v>
@@ -8042,7 +8066,7 @@
         <v>548</v>
       </c>
       <c r="B266" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C266" t="s">
         <v>549</v>
@@ -8059,13 +8083,13 @@
         <v>550</v>
       </c>
       <c r="B267" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C267" t="s">
         <v>551</v>
       </c>
       <c r="D267" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E267" t="s">
         <v>9</v>
@@ -8076,13 +8100,13 @@
         <v>552</v>
       </c>
       <c r="B268" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C268" t="s">
         <v>553</v>
       </c>
       <c r="D268" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E268" t="s">
         <v>9</v>
@@ -8093,13 +8117,13 @@
         <v>554</v>
       </c>
       <c r="B269" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C269" t="s">
         <v>555</v>
       </c>
       <c r="D269" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E269" t="s">
         <v>9</v>
@@ -8110,13 +8134,13 @@
         <v>556</v>
       </c>
       <c r="B270" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C270" t="s">
         <v>557</v>
       </c>
       <c r="D270" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E270" t="s">
         <v>9</v>
@@ -8127,13 +8151,13 @@
         <v>558</v>
       </c>
       <c r="B271" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C271" t="s">
         <v>559</v>
       </c>
       <c r="D271" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E271" t="s">
         <v>9</v>
@@ -8144,7 +8168,7 @@
         <v>560</v>
       </c>
       <c r="B272" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C272" t="s">
         <v>561</v>
@@ -8161,13 +8185,13 @@
         <v>562</v>
       </c>
       <c r="B273" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C273" t="s">
         <v>563</v>
       </c>
       <c r="D273" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E273" t="s">
         <v>9</v>
@@ -8178,13 +8202,13 @@
         <v>564</v>
       </c>
       <c r="B274" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C274" t="s">
         <v>565</v>
       </c>
       <c r="D274" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E274" t="s">
         <v>9</v>
@@ -8195,13 +8219,13 @@
         <v>566</v>
       </c>
       <c r="B275" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C275" t="s">
         <v>567</v>
       </c>
       <c r="D275" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E275" t="s">
         <v>9</v>
@@ -8212,13 +8236,13 @@
         <v>568</v>
       </c>
       <c r="B276" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C276" t="s">
         <v>569</v>
       </c>
       <c r="D276" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E276" t="s">
         <v>9</v>
@@ -8229,13 +8253,13 @@
         <v>570</v>
       </c>
       <c r="B277" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C277" t="s">
         <v>571</v>
       </c>
       <c r="D277" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E277" t="s">
         <v>9</v>
@@ -8246,7 +8270,7 @@
         <v>572</v>
       </c>
       <c r="B278" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C278" t="s">
         <v>573</v>
@@ -8263,13 +8287,13 @@
         <v>574</v>
       </c>
       <c r="B279" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C279" t="s">
         <v>575</v>
       </c>
       <c r="D279" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E279" t="s">
         <v>9</v>
@@ -8280,10 +8304,10 @@
         <v>576</v>
       </c>
       <c r="B280" t="s">
+        <v>540</v>
+      </c>
+      <c r="C280" t="s">
         <v>577</v>
-      </c>
-      <c r="C280" t="s">
-        <v>578</v>
       </c>
       <c r="D280" t="s">
         <v>8</v>
@@ -8294,16 +8318,16 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
+        <v>578</v>
+      </c>
+      <c r="B281" t="s">
+        <v>540</v>
+      </c>
+      <c r="C281" t="s">
         <v>579</v>
       </c>
-      <c r="B281" t="s">
-        <v>577</v>
-      </c>
-      <c r="C281" t="s">
-        <v>580</v>
-      </c>
       <c r="D281" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E281" t="s">
         <v>9</v>
@@ -8311,16 +8335,16 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
+        <v>580</v>
+      </c>
+      <c r="B282" t="s">
         <v>581</v>
-      </c>
-      <c r="B282" t="s">
-        <v>577</v>
       </c>
       <c r="C282" t="s">
         <v>582</v>
       </c>
       <c r="D282" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E282" t="s">
         <v>9</v>
@@ -8331,13 +8355,13 @@
         <v>583</v>
       </c>
       <c r="B283" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C283" t="s">
         <v>584</v>
       </c>
       <c r="D283" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E283" t="s">
         <v>9</v>
@@ -8348,13 +8372,13 @@
         <v>585</v>
       </c>
       <c r="B284" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C284" t="s">
         <v>586</v>
       </c>
       <c r="D284" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E284" t="s">
         <v>9</v>
@@ -8365,13 +8389,13 @@
         <v>587</v>
       </c>
       <c r="B285" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C285" t="s">
         <v>588</v>
       </c>
       <c r="D285" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E285" t="s">
         <v>9</v>
@@ -8382,7 +8406,7 @@
         <v>589</v>
       </c>
       <c r="B286" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C286" t="s">
         <v>590</v>
@@ -8399,13 +8423,13 @@
         <v>591</v>
       </c>
       <c r="B287" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C287" t="s">
         <v>592</v>
       </c>
       <c r="D287" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E287" t="s">
         <v>9</v>
@@ -8416,13 +8440,13 @@
         <v>593</v>
       </c>
       <c r="B288" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C288" t="s">
         <v>594</v>
       </c>
       <c r="D288" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E288" t="s">
         <v>9</v>
@@ -8433,13 +8457,13 @@
         <v>595</v>
       </c>
       <c r="B289" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C289" t="s">
         <v>596</v>
       </c>
       <c r="D289" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E289" t="s">
         <v>9</v>
@@ -8450,13 +8474,13 @@
         <v>597</v>
       </c>
       <c r="B290" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C290" t="s">
         <v>598</v>
       </c>
       <c r="D290" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E290" t="s">
         <v>9</v>
@@ -8467,13 +8491,13 @@
         <v>599</v>
       </c>
       <c r="B291" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C291" t="s">
         <v>600</v>
       </c>
       <c r="D291" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E291" t="s">
         <v>9</v>
@@ -8484,7 +8508,7 @@
         <v>601</v>
       </c>
       <c r="B292" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C292" t="s">
         <v>602</v>
@@ -8501,13 +8525,13 @@
         <v>603</v>
       </c>
       <c r="B293" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C293" t="s">
         <v>604</v>
       </c>
       <c r="D293" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E293" t="s">
         <v>9</v>
@@ -8518,13 +8542,13 @@
         <v>605</v>
       </c>
       <c r="B294" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C294" t="s">
         <v>606</v>
       </c>
       <c r="D294" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E294" t="s">
         <v>9</v>
@@ -8535,13 +8559,13 @@
         <v>607</v>
       </c>
       <c r="B295" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C295" t="s">
         <v>608</v>
       </c>
       <c r="D295" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E295" t="s">
         <v>9</v>
@@ -8552,13 +8576,13 @@
         <v>609</v>
       </c>
       <c r="B296" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C296" t="s">
         <v>610</v>
       </c>
       <c r="D296" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E296" t="s">
         <v>9</v>
@@ -8569,13 +8593,13 @@
         <v>611</v>
       </c>
       <c r="B297" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C297" t="s">
         <v>612</v>
       </c>
       <c r="D297" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E297" t="s">
         <v>9</v>
@@ -8586,7 +8610,7 @@
         <v>613</v>
       </c>
       <c r="B298" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C298" t="s">
         <v>614</v>
@@ -8603,13 +8627,13 @@
         <v>615</v>
       </c>
       <c r="B299" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C299" t="s">
         <v>616</v>
       </c>
       <c r="D299" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E299" t="s">
         <v>9</v>
@@ -8620,13 +8644,13 @@
         <v>617</v>
       </c>
       <c r="B300" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C300" t="s">
         <v>618</v>
       </c>
       <c r="D300" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E300" t="s">
         <v>9</v>
@@ -8637,13 +8661,13 @@
         <v>619</v>
       </c>
       <c r="B301" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C301" t="s">
         <v>620</v>
       </c>
       <c r="D301" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E301" t="s">
         <v>9</v>
@@ -8654,13 +8678,13 @@
         <v>621</v>
       </c>
       <c r="B302" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C302" t="s">
         <v>622</v>
       </c>
       <c r="D302" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E302" t="s">
         <v>9</v>
@@ -8671,13 +8695,13 @@
         <v>623</v>
       </c>
       <c r="B303" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C303" t="s">
         <v>624</v>
       </c>
       <c r="D303" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E303" t="s">
         <v>9</v>
@@ -8688,7 +8712,7 @@
         <v>625</v>
       </c>
       <c r="B304" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C304" t="s">
         <v>626</v>
@@ -8705,13 +8729,13 @@
         <v>627</v>
       </c>
       <c r="B305" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C305" t="s">
         <v>628</v>
       </c>
       <c r="D305" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E305" t="s">
         <v>9</v>
@@ -8722,13 +8746,13 @@
         <v>629</v>
       </c>
       <c r="B306" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C306" t="s">
         <v>630</v>
       </c>
       <c r="D306" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E306" t="s">
         <v>9</v>
@@ -8739,13 +8763,13 @@
         <v>631</v>
       </c>
       <c r="B307" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C307" t="s">
         <v>632</v>
       </c>
       <c r="D307" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E307" t="s">
         <v>9</v>
@@ -8756,13 +8780,13 @@
         <v>633</v>
       </c>
       <c r="B308" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C308" t="s">
         <v>634</v>
       </c>
       <c r="D308" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E308" t="s">
         <v>9</v>
@@ -8773,13 +8797,13 @@
         <v>635</v>
       </c>
       <c r="B309" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C309" t="s">
         <v>636</v>
       </c>
       <c r="D309" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E309" t="s">
         <v>9</v>
@@ -8790,7 +8814,7 @@
         <v>637</v>
       </c>
       <c r="B310" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C310" t="s">
         <v>638</v>
@@ -8807,13 +8831,13 @@
         <v>639</v>
       </c>
       <c r="B311" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C311" t="s">
         <v>640</v>
       </c>
       <c r="D311" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E311" t="s">
         <v>9</v>
@@ -8824,13 +8848,13 @@
         <v>641</v>
       </c>
       <c r="B312" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C312" t="s">
         <v>642</v>
       </c>
       <c r="D312" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E312" t="s">
         <v>9</v>
@@ -8841,13 +8865,13 @@
         <v>643</v>
       </c>
       <c r="B313" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C313" t="s">
         <v>644</v>
       </c>
       <c r="D313" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E313" t="s">
         <v>9</v>
@@ -8858,13 +8882,13 @@
         <v>645</v>
       </c>
       <c r="B314" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C314" t="s">
         <v>646</v>
       </c>
       <c r="D314" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E314" t="s">
         <v>9</v>
@@ -8875,13 +8899,13 @@
         <v>647</v>
       </c>
       <c r="B315" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C315" t="s">
         <v>648</v>
       </c>
       <c r="D315" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E315" t="s">
         <v>9</v>
@@ -8892,7 +8916,7 @@
         <v>649</v>
       </c>
       <c r="B316" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C316" t="s">
         <v>650</v>
@@ -8909,13 +8933,13 @@
         <v>651</v>
       </c>
       <c r="B317" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C317" t="s">
         <v>652</v>
       </c>
       <c r="D317" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E317" t="s">
         <v>9</v>
@@ -8926,13 +8950,13 @@
         <v>653</v>
       </c>
       <c r="B318" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C318" t="s">
         <v>654</v>
       </c>
       <c r="D318" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E318" t="s">
         <v>9</v>
@@ -8943,13 +8967,13 @@
         <v>655</v>
       </c>
       <c r="B319" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C319" t="s">
         <v>656</v>
       </c>
       <c r="D319" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E319" t="s">
         <v>9</v>
@@ -8960,13 +8984,13 @@
         <v>657</v>
       </c>
       <c r="B320" t="s">
+        <v>581</v>
+      </c>
+      <c r="C320" t="s">
         <v>658</v>
       </c>
-      <c r="C320" t="s">
-        <v>659</v>
-      </c>
       <c r="D320" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E320" t="s">
         <v>9</v>
@@ -8974,16 +8998,16 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
+        <v>659</v>
+      </c>
+      <c r="B321" t="s">
+        <v>581</v>
+      </c>
+      <c r="C321" t="s">
         <v>660</v>
       </c>
-      <c r="B321" t="s">
-        <v>658</v>
-      </c>
-      <c r="C321" t="s">
-        <v>661</v>
-      </c>
       <c r="D321" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E321" t="s">
         <v>9</v>
@@ -8991,16 +9015,16 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
+        <v>661</v>
+      </c>
+      <c r="B322" t="s">
         <v>662</v>
-      </c>
-      <c r="B322" t="s">
-        <v>658</v>
       </c>
       <c r="C322" t="s">
         <v>663</v>
       </c>
       <c r="D322" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E322" t="s">
         <v>9</v>
@@ -9011,13 +9035,13 @@
         <v>664</v>
       </c>
       <c r="B323" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C323" t="s">
         <v>665</v>
       </c>
       <c r="D323" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E323" t="s">
         <v>9</v>
@@ -9028,13 +9052,13 @@
         <v>666</v>
       </c>
       <c r="B324" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C324" t="s">
         <v>667</v>
       </c>
       <c r="D324" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E324" t="s">
         <v>9</v>
@@ -9045,13 +9069,13 @@
         <v>668</v>
       </c>
       <c r="B325" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C325" t="s">
         <v>669</v>
       </c>
       <c r="D325" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E325" t="s">
         <v>9</v>
@@ -9062,7 +9086,7 @@
         <v>670</v>
       </c>
       <c r="B326" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C326" t="s">
         <v>671</v>
@@ -9079,13 +9103,13 @@
         <v>672</v>
       </c>
       <c r="B327" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C327" t="s">
         <v>673</v>
       </c>
       <c r="D327" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E327" t="s">
         <v>9</v>
@@ -9096,13 +9120,13 @@
         <v>674</v>
       </c>
       <c r="B328" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C328" t="s">
         <v>675</v>
       </c>
       <c r="D328" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E328" t="s">
         <v>9</v>
@@ -9113,13 +9137,13 @@
         <v>676</v>
       </c>
       <c r="B329" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C329" t="s">
         <v>677</v>
       </c>
       <c r="D329" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E329" t="s">
         <v>9</v>
@@ -9130,13 +9154,13 @@
         <v>678</v>
       </c>
       <c r="B330" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C330" t="s">
         <v>679</v>
       </c>
       <c r="D330" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E330" t="s">
         <v>9</v>
@@ -9147,13 +9171,13 @@
         <v>680</v>
       </c>
       <c r="B331" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C331" t="s">
         <v>681</v>
       </c>
       <c r="D331" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E331" t="s">
         <v>9</v>
@@ -9164,7 +9188,7 @@
         <v>682</v>
       </c>
       <c r="B332" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C332" t="s">
         <v>683</v>
@@ -9181,13 +9205,13 @@
         <v>684</v>
       </c>
       <c r="B333" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C333" t="s">
         <v>685</v>
       </c>
       <c r="D333" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E333" t="s">
         <v>9</v>
@@ -9198,13 +9222,13 @@
         <v>686</v>
       </c>
       <c r="B334" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C334" t="s">
         <v>687</v>
       </c>
       <c r="D334" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E334" t="s">
         <v>9</v>
@@ -9215,13 +9239,13 @@
         <v>688</v>
       </c>
       <c r="B335" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C335" t="s">
         <v>689</v>
       </c>
       <c r="D335" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E335" t="s">
         <v>9</v>
@@ -9232,13 +9256,13 @@
         <v>690</v>
       </c>
       <c r="B336" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C336" t="s">
         <v>691</v>
       </c>
       <c r="D336" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E336" t="s">
         <v>9</v>
@@ -9249,13 +9273,13 @@
         <v>692</v>
       </c>
       <c r="B337" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C337" t="s">
         <v>693</v>
       </c>
       <c r="D337" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E337" t="s">
         <v>9</v>
@@ -9266,7 +9290,7 @@
         <v>694</v>
       </c>
       <c r="B338" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C338" t="s">
         <v>695</v>
@@ -9283,13 +9307,13 @@
         <v>696</v>
       </c>
       <c r="B339" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C339" t="s">
         <v>697</v>
       </c>
       <c r="D339" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E339" t="s">
         <v>9</v>
@@ -9300,10 +9324,10 @@
         <v>698</v>
       </c>
       <c r="B340" t="s">
+        <v>662</v>
+      </c>
+      <c r="C340" t="s">
         <v>699</v>
-      </c>
-      <c r="C340" t="s">
-        <v>700</v>
       </c>
       <c r="D340" t="s">
         <v>8</v>
@@ -9314,16 +9338,16 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
+        <v>700</v>
+      </c>
+      <c r="B341" t="s">
+        <v>662</v>
+      </c>
+      <c r="C341" t="s">
         <v>701</v>
       </c>
-      <c r="B341" t="s">
-        <v>699</v>
-      </c>
-      <c r="C341" t="s">
-        <v>702</v>
-      </c>
       <c r="D341" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E341" t="s">
         <v>9</v>
@@ -9331,16 +9355,16 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
+        <v>702</v>
+      </c>
+      <c r="B342" t="s">
         <v>703</v>
-      </c>
-      <c r="B342" t="s">
-        <v>699</v>
       </c>
       <c r="C342" t="s">
         <v>704</v>
       </c>
       <c r="D342" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E342" t="s">
         <v>9</v>
@@ -9351,13 +9375,13 @@
         <v>705</v>
       </c>
       <c r="B343" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C343" t="s">
         <v>706</v>
       </c>
       <c r="D343" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E343" t="s">
         <v>9</v>
@@ -9368,13 +9392,13 @@
         <v>707</v>
       </c>
       <c r="B344" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C344" t="s">
         <v>708</v>
       </c>
       <c r="D344" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E344" t="s">
         <v>9</v>
@@ -9385,13 +9409,13 @@
         <v>709</v>
       </c>
       <c r="B345" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C345" t="s">
         <v>710</v>
       </c>
       <c r="D345" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E345" t="s">
         <v>9</v>
@@ -9402,7 +9426,7 @@
         <v>711</v>
       </c>
       <c r="B346" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C346" t="s">
         <v>712</v>
@@ -9419,13 +9443,13 @@
         <v>713</v>
       </c>
       <c r="B347" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C347" t="s">
         <v>714</v>
       </c>
       <c r="D347" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E347" t="s">
         <v>9</v>
@@ -9436,13 +9460,13 @@
         <v>715</v>
       </c>
       <c r="B348" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C348" t="s">
         <v>716</v>
       </c>
       <c r="D348" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E348" t="s">
         <v>9</v>
@@ -9453,13 +9477,13 @@
         <v>717</v>
       </c>
       <c r="B349" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C349" t="s">
         <v>718</v>
       </c>
       <c r="D349" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E349" t="s">
         <v>9</v>
@@ -9470,13 +9494,13 @@
         <v>719</v>
       </c>
       <c r="B350" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C350" t="s">
         <v>720</v>
       </c>
       <c r="D350" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E350" t="s">
         <v>9</v>
@@ -9487,13 +9511,13 @@
         <v>721</v>
       </c>
       <c r="B351" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C351" t="s">
         <v>722</v>
       </c>
       <c r="D351" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E351" t="s">
         <v>9</v>
@@ -9504,7 +9528,7 @@
         <v>723</v>
       </c>
       <c r="B352" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C352" t="s">
         <v>724</v>
@@ -9521,13 +9545,13 @@
         <v>725</v>
       </c>
       <c r="B353" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C353" t="s">
         <v>726</v>
       </c>
       <c r="D353" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E353" t="s">
         <v>9</v>
@@ -9538,13 +9562,13 @@
         <v>727</v>
       </c>
       <c r="B354" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C354" t="s">
         <v>728</v>
       </c>
       <c r="D354" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E354" t="s">
         <v>9</v>
@@ -9555,13 +9579,13 @@
         <v>729</v>
       </c>
       <c r="B355" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C355" t="s">
         <v>730</v>
       </c>
       <c r="D355" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E355" t="s">
         <v>9</v>
@@ -9572,13 +9596,13 @@
         <v>731</v>
       </c>
       <c r="B356" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C356" t="s">
         <v>732</v>
       </c>
       <c r="D356" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E356" t="s">
         <v>9</v>
@@ -9589,13 +9613,13 @@
         <v>733</v>
       </c>
       <c r="B357" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C357" t="s">
         <v>734</v>
       </c>
       <c r="D357" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E357" t="s">
         <v>9</v>
@@ -9606,7 +9630,7 @@
         <v>735</v>
       </c>
       <c r="B358" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C358" t="s">
         <v>736</v>
@@ -9623,13 +9647,13 @@
         <v>737</v>
       </c>
       <c r="B359" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C359" t="s">
         <v>738</v>
       </c>
       <c r="D359" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E359" t="s">
         <v>9</v>
@@ -9640,10 +9664,10 @@
         <v>739</v>
       </c>
       <c r="B360" t="s">
+        <v>703</v>
+      </c>
+      <c r="C360" t="s">
         <v>740</v>
-      </c>
-      <c r="C360" t="s">
-        <v>741</v>
       </c>
       <c r="D360" t="s">
         <v>8</v>
@@ -9654,16 +9678,16 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
+        <v>741</v>
+      </c>
+      <c r="B361" t="s">
+        <v>703</v>
+      </c>
+      <c r="C361" t="s">
         <v>742</v>
       </c>
-      <c r="B361" t="s">
-        <v>740</v>
-      </c>
-      <c r="C361" t="s">
-        <v>743</v>
-      </c>
       <c r="D361" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E361" t="s">
         <v>9</v>
@@ -9671,16 +9695,16 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
+        <v>743</v>
+      </c>
+      <c r="B362" t="s">
         <v>744</v>
-      </c>
-      <c r="B362" t="s">
-        <v>740</v>
       </c>
       <c r="C362" t="s">
         <v>745</v>
       </c>
       <c r="D362" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E362" t="s">
         <v>9</v>
@@ -9691,13 +9715,13 @@
         <v>746</v>
       </c>
       <c r="B363" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C363" t="s">
         <v>747</v>
       </c>
       <c r="D363" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E363" t="s">
         <v>9</v>
@@ -9708,7 +9732,7 @@
         <v>748</v>
       </c>
       <c r="B364" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C364" t="s">
         <v>749</v>
@@ -9725,13 +9749,13 @@
         <v>750</v>
       </c>
       <c r="B365" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C365" t="s">
         <v>751</v>
       </c>
       <c r="D365" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E365" t="s">
         <v>9</v>
@@ -9742,13 +9766,13 @@
         <v>752</v>
       </c>
       <c r="B366" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C366" t="s">
         <v>753</v>
       </c>
       <c r="D366" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E366" t="s">
         <v>9</v>
@@ -9759,7 +9783,7 @@
         <v>754</v>
       </c>
       <c r="B367" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C367" t="s">
         <v>755</v>
@@ -9776,13 +9800,13 @@
         <v>756</v>
       </c>
       <c r="B368" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C368" t="s">
         <v>757</v>
       </c>
       <c r="D368" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E368" t="s">
         <v>9</v>
@@ -9793,13 +9817,13 @@
         <v>758</v>
       </c>
       <c r="B369" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C369" t="s">
         <v>759</v>
       </c>
       <c r="D369" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E369" t="s">
         <v>9</v>
@@ -9810,13 +9834,13 @@
         <v>760</v>
       </c>
       <c r="B370" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C370" t="s">
         <v>761</v>
       </c>
       <c r="D370" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E370" t="s">
         <v>9</v>
@@ -9827,13 +9851,13 @@
         <v>762</v>
       </c>
       <c r="B371" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C371" t="s">
         <v>763</v>
       </c>
       <c r="D371" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E371" t="s">
         <v>9</v>
@@ -9844,13 +9868,13 @@
         <v>764</v>
       </c>
       <c r="B372" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C372" t="s">
         <v>765</v>
       </c>
       <c r="D372" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E372" t="s">
         <v>9</v>
@@ -9861,13 +9885,13 @@
         <v>766</v>
       </c>
       <c r="B373" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C373" t="s">
         <v>767</v>
       </c>
       <c r="D373" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E373" t="s">
         <v>9</v>
@@ -9878,13 +9902,13 @@
         <v>768</v>
       </c>
       <c r="B374" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C374" t="s">
         <v>769</v>
       </c>
       <c r="D374" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E374" t="s">
         <v>9</v>
@@ -9895,13 +9919,13 @@
         <v>770</v>
       </c>
       <c r="B375" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C375" t="s">
         <v>771</v>
       </c>
       <c r="D375" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E375" t="s">
         <v>9</v>
@@ -9912,7 +9936,7 @@
         <v>772</v>
       </c>
       <c r="B376" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C376" t="s">
         <v>773</v>
@@ -9929,13 +9953,13 @@
         <v>774</v>
       </c>
       <c r="B377" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C377" t="s">
         <v>775</v>
       </c>
       <c r="D377" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E377" t="s">
         <v>9</v>
@@ -9946,13 +9970,13 @@
         <v>776</v>
       </c>
       <c r="B378" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C378" t="s">
         <v>777</v>
       </c>
       <c r="D378" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E378" t="s">
         <v>9</v>
@@ -9963,13 +9987,13 @@
         <v>778</v>
       </c>
       <c r="B379" t="s">
+        <v>744</v>
+      </c>
+      <c r="C379" t="s">
         <v>779</v>
       </c>
-      <c r="C379" t="s">
-        <v>780</v>
-      </c>
       <c r="D379" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E379" t="s">
         <v>9</v>
@@ -9977,16 +10001,16 @@
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
+        <v>780</v>
+      </c>
+      <c r="B380" t="s">
+        <v>744</v>
+      </c>
+      <c r="C380" t="s">
         <v>781</v>
       </c>
-      <c r="B380" t="s">
-        <v>779</v>
-      </c>
-      <c r="C380" t="s">
-        <v>782</v>
-      </c>
       <c r="D380" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E380" t="s">
         <v>9</v>
@@ -9994,13 +10018,13 @@
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
+        <v>782</v>
+      </c>
+      <c r="B381" t="s">
+        <v>744</v>
+      </c>
+      <c r="C381" t="s">
         <v>783</v>
-      </c>
-      <c r="B381" t="s">
-        <v>779</v>
-      </c>
-      <c r="C381" t="s">
-        <v>784</v>
       </c>
       <c r="D381" t="s">
         <v>18</v>
@@ -10011,10 +10035,10 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
+        <v>784</v>
+      </c>
+      <c r="B382" t="s">
         <v>785</v>
-      </c>
-      <c r="B382" t="s">
-        <v>779</v>
       </c>
       <c r="C382" t="s">
         <v>786</v>
@@ -10031,13 +10055,13 @@
         <v>787</v>
       </c>
       <c r="B383" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="C383" t="s">
         <v>788</v>
       </c>
       <c r="D383" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E383" t="s">
         <v>9</v>
@@ -10048,13 +10072,13 @@
         <v>789</v>
       </c>
       <c r="B384" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="C384" t="s">
         <v>790</v>
       </c>
       <c r="D384" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E384" t="s">
         <v>9</v>
@@ -10065,7 +10089,7 @@
         <v>791</v>
       </c>
       <c r="B385" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="C385" t="s">
         <v>792</v>
@@ -10082,13 +10106,13 @@
         <v>793</v>
       </c>
       <c r="B386" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="C386" t="s">
         <v>794</v>
       </c>
       <c r="D386" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E386" t="s">
         <v>9</v>
@@ -10099,13 +10123,13 @@
         <v>795</v>
       </c>
       <c r="B387" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="C387" t="s">
         <v>796</v>
       </c>
       <c r="D387" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E387" t="s">
         <v>9</v>
@@ -10116,7 +10140,7 @@
         <v>797</v>
       </c>
       <c r="B388" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="C388" t="s">
         <v>798</v>
@@ -10133,7 +10157,7 @@
         <v>799</v>
       </c>
       <c r="B389" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="C389" t="s">
         <v>800</v>
@@ -10150,13 +10174,13 @@
         <v>801</v>
       </c>
       <c r="B390" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="C390" t="s">
         <v>802</v>
       </c>
       <c r="D390" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E390" t="s">
         <v>9</v>
@@ -10167,7 +10191,7 @@
         <v>803</v>
       </c>
       <c r="B391" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="C391" t="s">
         <v>804</v>
@@ -10184,13 +10208,13 @@
         <v>805</v>
       </c>
       <c r="B392" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="C392" t="s">
         <v>806</v>
       </c>
       <c r="D392" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E392" t="s">
         <v>9</v>
@@ -10201,7 +10225,7 @@
         <v>807</v>
       </c>
       <c r="B393" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="C393" t="s">
         <v>808</v>
@@ -10218,7 +10242,7 @@
         <v>809</v>
       </c>
       <c r="B394" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="C394" t="s">
         <v>810</v>
@@ -10235,13 +10259,13 @@
         <v>811</v>
       </c>
       <c r="B395" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="C395" t="s">
         <v>812</v>
       </c>
       <c r="D395" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E395" t="s">
         <v>9</v>
@@ -10252,13 +10276,13 @@
         <v>813</v>
       </c>
       <c r="B396" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="C396" t="s">
         <v>814</v>
       </c>
       <c r="D396" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E396" t="s">
         <v>9</v>
@@ -10269,7 +10293,7 @@
         <v>815</v>
       </c>
       <c r="B397" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="C397" t="s">
         <v>816</v>
@@ -10286,10 +10310,10 @@
         <v>817</v>
       </c>
       <c r="B398" t="s">
+        <v>785</v>
+      </c>
+      <c r="C398" t="s">
         <v>818</v>
-      </c>
-      <c r="C398" t="s">
-        <v>819</v>
       </c>
       <c r="D398" t="s">
         <v>8</v>
@@ -10300,16 +10324,16 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
+        <v>819</v>
+      </c>
+      <c r="B399" t="s">
+        <v>785</v>
+      </c>
+      <c r="C399" t="s">
         <v>820</v>
       </c>
-      <c r="B399" t="s">
-        <v>818</v>
-      </c>
-      <c r="C399" t="s">
-        <v>821</v>
-      </c>
       <c r="D399" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E399" t="s">
         <v>9</v>
@@ -10317,16 +10341,16 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
+        <v>821</v>
+      </c>
+      <c r="B400" t="s">
+        <v>785</v>
+      </c>
+      <c r="C400" t="s">
         <v>822</v>
       </c>
-      <c r="B400" t="s">
-        <v>818</v>
-      </c>
-      <c r="C400" t="s">
-        <v>823</v>
-      </c>
       <c r="D400" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E400" t="s">
         <v>9</v>
@@ -10334,13 +10358,13 @@
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
+        <v>823</v>
+      </c>
+      <c r="B401" t="s">
+        <v>785</v>
+      </c>
+      <c r="C401" t="s">
         <v>824</v>
-      </c>
-      <c r="B401" t="s">
-        <v>818</v>
-      </c>
-      <c r="C401" t="s">
-        <v>825</v>
       </c>
       <c r="D401" t="s">
         <v>18</v>
@@ -10351,10 +10375,10 @@
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
+        <v>825</v>
+      </c>
+      <c r="B402" t="s">
         <v>826</v>
-      </c>
-      <c r="B402" t="s">
-        <v>818</v>
       </c>
       <c r="C402" t="s">
         <v>827</v>
@@ -10371,13 +10395,13 @@
         <v>828</v>
       </c>
       <c r="B403" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="C403" t="s">
         <v>829</v>
       </c>
       <c r="D403" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E403" t="s">
         <v>9</v>
@@ -10388,13 +10412,13 @@
         <v>830</v>
       </c>
       <c r="B404" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="C404" t="s">
         <v>831</v>
       </c>
       <c r="D404" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E404" t="s">
         <v>9</v>
@@ -10405,7 +10429,7 @@
         <v>832</v>
       </c>
       <c r="B405" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="C405" t="s">
         <v>833</v>
@@ -10422,13 +10446,13 @@
         <v>834</v>
       </c>
       <c r="B406" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="C406" t="s">
         <v>835</v>
       </c>
       <c r="D406" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E406" t="s">
         <v>9</v>
@@ -10439,13 +10463,13 @@
         <v>836</v>
       </c>
       <c r="B407" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="C407" t="s">
         <v>837</v>
       </c>
       <c r="D407" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E407" t="s">
         <v>9</v>
@@ -10456,10 +10480,10 @@
         <v>838</v>
       </c>
       <c r="B408" t="s">
+        <v>826</v>
+      </c>
+      <c r="C408" t="s">
         <v>839</v>
-      </c>
-      <c r="C408" t="s">
-        <v>840</v>
       </c>
       <c r="D408" t="s">
         <v>8</v>
@@ -10470,16 +10494,16 @@
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
+        <v>840</v>
+      </c>
+      <c r="B409" t="s">
+        <v>826</v>
+      </c>
+      <c r="C409" t="s">
         <v>841</v>
       </c>
-      <c r="B409" t="s">
-        <v>839</v>
-      </c>
-      <c r="C409" t="s">
-        <v>842</v>
-      </c>
       <c r="D409" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E409" t="s">
         <v>9</v>
@@ -10487,13 +10511,13 @@
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
+        <v>842</v>
+      </c>
+      <c r="B410" t="s">
+        <v>826</v>
+      </c>
+      <c r="C410" t="s">
         <v>843</v>
-      </c>
-      <c r="B410" t="s">
-        <v>839</v>
-      </c>
-      <c r="C410" t="s">
-        <v>844</v>
       </c>
       <c r="D410" t="s">
         <v>15</v>
@@ -10504,16 +10528,16 @@
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
+        <v>844</v>
+      </c>
+      <c r="B411" t="s">
+        <v>826</v>
+      </c>
+      <c r="C411" t="s">
         <v>845</v>
       </c>
-      <c r="B411" t="s">
-        <v>839</v>
-      </c>
-      <c r="C411" t="s">
-        <v>846</v>
-      </c>
       <c r="D411" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E411" t="s">
         <v>9</v>
@@ -10521,10 +10545,10 @@
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
+        <v>846</v>
+      </c>
+      <c r="B412" t="s">
         <v>847</v>
-      </c>
-      <c r="B412" t="s">
-        <v>839</v>
       </c>
       <c r="C412" t="s">
         <v>848</v>
@@ -10541,13 +10565,13 @@
         <v>849</v>
       </c>
       <c r="B413" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C413" t="s">
         <v>850</v>
       </c>
       <c r="D413" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E413" t="s">
         <v>9</v>
@@ -10558,13 +10582,13 @@
         <v>851</v>
       </c>
       <c r="B414" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C414" t="s">
         <v>852</v>
       </c>
       <c r="D414" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E414" t="s">
         <v>9</v>
@@ -10575,7 +10599,7 @@
         <v>853</v>
       </c>
       <c r="B415" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C415" t="s">
         <v>854</v>
@@ -10592,13 +10616,13 @@
         <v>855</v>
       </c>
       <c r="B416" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C416" t="s">
         <v>856</v>
       </c>
       <c r="D416" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E416" t="s">
         <v>9</v>
@@ -10609,13 +10633,13 @@
         <v>857</v>
       </c>
       <c r="B417" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C417" t="s">
         <v>858</v>
       </c>
       <c r="D417" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E417" t="s">
         <v>9</v>
@@ -10626,7 +10650,7 @@
         <v>859</v>
       </c>
       <c r="B418" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C418" t="s">
         <v>860</v>
@@ -10643,7 +10667,7 @@
         <v>861</v>
       </c>
       <c r="B419" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C419" t="s">
         <v>862</v>
@@ -10660,13 +10684,13 @@
         <v>863</v>
       </c>
       <c r="B420" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C420" t="s">
         <v>864</v>
       </c>
       <c r="D420" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E420" t="s">
         <v>9</v>
@@ -10677,7 +10701,7 @@
         <v>865</v>
       </c>
       <c r="B421" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C421" t="s">
         <v>866</v>
@@ -10694,13 +10718,13 @@
         <v>867</v>
       </c>
       <c r="B422" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C422" t="s">
         <v>868</v>
       </c>
       <c r="D422" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E422" t="s">
         <v>9</v>
@@ -10711,7 +10735,7 @@
         <v>869</v>
       </c>
       <c r="B423" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C423" t="s">
         <v>870</v>
@@ -10728,7 +10752,7 @@
         <v>871</v>
       </c>
       <c r="B424" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C424" t="s">
         <v>872</v>
@@ -10745,13 +10769,13 @@
         <v>873</v>
       </c>
       <c r="B425" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C425" t="s">
         <v>874</v>
       </c>
       <c r="D425" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E425" t="s">
         <v>9</v>
@@ -10762,13 +10786,13 @@
         <v>875</v>
       </c>
       <c r="B426" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C426" t="s">
         <v>876</v>
       </c>
       <c r="D426" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E426" t="s">
         <v>9</v>
@@ -10779,7 +10803,7 @@
         <v>877</v>
       </c>
       <c r="B427" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C427" t="s">
         <v>878</v>
@@ -10796,10 +10820,10 @@
         <v>879</v>
       </c>
       <c r="B428" t="s">
+        <v>847</v>
+      </c>
+      <c r="C428" t="s">
         <v>880</v>
-      </c>
-      <c r="C428" t="s">
-        <v>881</v>
       </c>
       <c r="D428" t="s">
         <v>8</v>
@@ -10810,16 +10834,16 @@
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
+        <v>881</v>
+      </c>
+      <c r="B429" t="s">
+        <v>847</v>
+      </c>
+      <c r="C429" t="s">
         <v>882</v>
       </c>
-      <c r="B429" t="s">
-        <v>880</v>
-      </c>
-      <c r="C429" t="s">
-        <v>883</v>
-      </c>
       <c r="D429" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E429" t="s">
         <v>9</v>
@@ -10827,16 +10851,16 @@
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
+        <v>883</v>
+      </c>
+      <c r="B430" t="s">
+        <v>847</v>
+      </c>
+      <c r="C430" t="s">
         <v>884</v>
       </c>
-      <c r="B430" t="s">
-        <v>880</v>
-      </c>
-      <c r="C430" t="s">
-        <v>885</v>
-      </c>
       <c r="D430" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E430" t="s">
         <v>9</v>
@@ -10844,13 +10868,13 @@
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
+        <v>885</v>
+      </c>
+      <c r="B431" t="s">
+        <v>847</v>
+      </c>
+      <c r="C431" t="s">
         <v>886</v>
-      </c>
-      <c r="B431" t="s">
-        <v>880</v>
-      </c>
-      <c r="C431" t="s">
-        <v>887</v>
       </c>
       <c r="D431" t="s">
         <v>18</v>
@@ -10861,10 +10885,10 @@
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
+        <v>887</v>
+      </c>
+      <c r="B432" t="s">
         <v>888</v>
-      </c>
-      <c r="B432" t="s">
-        <v>880</v>
       </c>
       <c r="C432" t="s">
         <v>889</v>
@@ -10881,13 +10905,13 @@
         <v>890</v>
       </c>
       <c r="B433" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="C433" t="s">
         <v>891</v>
       </c>
       <c r="D433" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E433" t="s">
         <v>9</v>
@@ -10898,13 +10922,13 @@
         <v>892</v>
       </c>
       <c r="B434" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="C434" t="s">
         <v>893</v>
       </c>
       <c r="D434" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E434" t="s">
         <v>9</v>
@@ -10915,7 +10939,7 @@
         <v>894</v>
       </c>
       <c r="B435" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="C435" t="s">
         <v>895</v>
@@ -10932,13 +10956,13 @@
         <v>896</v>
       </c>
       <c r="B436" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="C436" t="s">
         <v>897</v>
       </c>
       <c r="D436" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E436" t="s">
         <v>9</v>
@@ -10949,13 +10973,13 @@
         <v>898</v>
       </c>
       <c r="B437" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="C437" t="s">
         <v>899</v>
       </c>
       <c r="D437" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E437" t="s">
         <v>9</v>
@@ -10966,10 +10990,10 @@
         <v>900</v>
       </c>
       <c r="B438" t="s">
+        <v>888</v>
+      </c>
+      <c r="C438" t="s">
         <v>901</v>
-      </c>
-      <c r="C438" t="s">
-        <v>902</v>
       </c>
       <c r="D438" t="s">
         <v>8</v>
@@ -10980,16 +11004,16 @@
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
+        <v>902</v>
+      </c>
+      <c r="B439" t="s">
+        <v>888</v>
+      </c>
+      <c r="C439" t="s">
         <v>903</v>
       </c>
-      <c r="B439" t="s">
-        <v>901</v>
-      </c>
-      <c r="C439" t="s">
-        <v>904</v>
-      </c>
       <c r="D439" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E439" t="s">
         <v>9</v>
@@ -10997,13 +11021,13 @@
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
+        <v>904</v>
+      </c>
+      <c r="B440" t="s">
+        <v>888</v>
+      </c>
+      <c r="C440" t="s">
         <v>905</v>
-      </c>
-      <c r="B440" t="s">
-        <v>901</v>
-      </c>
-      <c r="C440" t="s">
-        <v>906</v>
       </c>
       <c r="D440" t="s">
         <v>15</v>
@@ -11014,16 +11038,16 @@
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
+        <v>906</v>
+      </c>
+      <c r="B441" t="s">
+        <v>888</v>
+      </c>
+      <c r="C441" t="s">
         <v>907</v>
       </c>
-      <c r="B441" t="s">
-        <v>901</v>
-      </c>
-      <c r="C441" t="s">
-        <v>908</v>
-      </c>
       <c r="D441" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E441" t="s">
         <v>9</v>
@@ -11031,10 +11055,10 @@
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
+        <v>908</v>
+      </c>
+      <c r="B442" t="s">
         <v>909</v>
-      </c>
-      <c r="B442" t="s">
-        <v>901</v>
       </c>
       <c r="C442" t="s">
         <v>910</v>
@@ -11051,13 +11075,13 @@
         <v>911</v>
       </c>
       <c r="B443" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="C443" t="s">
         <v>912</v>
       </c>
       <c r="D443" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E443" t="s">
         <v>9</v>
@@ -11068,13 +11092,13 @@
         <v>913</v>
       </c>
       <c r="B444" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="C444" t="s">
         <v>914</v>
       </c>
       <c r="D444" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E444" t="s">
         <v>9</v>
@@ -11085,7 +11109,7 @@
         <v>915</v>
       </c>
       <c r="B445" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="C445" t="s">
         <v>916</v>
@@ -11102,13 +11126,13 @@
         <v>917</v>
       </c>
       <c r="B446" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="C446" t="s">
         <v>918</v>
       </c>
       <c r="D446" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E446" t="s">
         <v>9</v>
@@ -11119,13 +11143,13 @@
         <v>919</v>
       </c>
       <c r="B447" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="C447" t="s">
         <v>920</v>
       </c>
       <c r="D447" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E447" t="s">
         <v>9</v>
@@ -11136,7 +11160,7 @@
         <v>921</v>
       </c>
       <c r="B448" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="C448" t="s">
         <v>922</v>
@@ -11153,7 +11177,7 @@
         <v>923</v>
       </c>
       <c r="B449" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="C449" t="s">
         <v>924</v>
@@ -11170,13 +11194,13 @@
         <v>925</v>
       </c>
       <c r="B450" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="C450" t="s">
         <v>926</v>
       </c>
       <c r="D450" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E450" t="s">
         <v>9</v>
@@ -11187,7 +11211,7 @@
         <v>927</v>
       </c>
       <c r="B451" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="C451" t="s">
         <v>928</v>
@@ -11204,13 +11228,13 @@
         <v>929</v>
       </c>
       <c r="B452" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="C452" t="s">
         <v>930</v>
       </c>
       <c r="D452" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E452" t="s">
         <v>9</v>
@@ -11221,7 +11245,7 @@
         <v>931</v>
       </c>
       <c r="B453" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="C453" t="s">
         <v>932</v>
@@ -11238,7 +11262,7 @@
         <v>933</v>
       </c>
       <c r="B454" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="C454" t="s">
         <v>934</v>
@@ -11255,13 +11279,13 @@
         <v>935</v>
       </c>
       <c r="B455" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="C455" t="s">
         <v>936</v>
       </c>
       <c r="D455" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E455" t="s">
         <v>9</v>
@@ -11272,13 +11296,13 @@
         <v>937</v>
       </c>
       <c r="B456" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="C456" t="s">
         <v>938</v>
       </c>
       <c r="D456" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E456" t="s">
         <v>9</v>
@@ -11289,7 +11313,7 @@
         <v>939</v>
       </c>
       <c r="B457" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="C457" t="s">
         <v>940</v>
@@ -11306,10 +11330,10 @@
         <v>941</v>
       </c>
       <c r="B458" t="s">
+        <v>909</v>
+      </c>
+      <c r="C458" t="s">
         <v>942</v>
-      </c>
-      <c r="C458" t="s">
-        <v>943</v>
       </c>
       <c r="D458" t="s">
         <v>8</v>
@@ -11320,16 +11344,16 @@
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
+        <v>943</v>
+      </c>
+      <c r="B459" t="s">
+        <v>909</v>
+      </c>
+      <c r="C459" t="s">
         <v>944</v>
       </c>
-      <c r="B459" t="s">
-        <v>942</v>
-      </c>
-      <c r="C459" t="s">
-        <v>945</v>
-      </c>
       <c r="D459" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E459" t="s">
         <v>9</v>
@@ -11337,16 +11361,16 @@
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
+        <v>945</v>
+      </c>
+      <c r="B460" t="s">
+        <v>909</v>
+      </c>
+      <c r="C460" t="s">
         <v>946</v>
       </c>
-      <c r="B460" t="s">
-        <v>942</v>
-      </c>
-      <c r="C460" t="s">
-        <v>947</v>
-      </c>
       <c r="D460" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E460" t="s">
         <v>9</v>
@@ -11354,13 +11378,13 @@
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
+        <v>947</v>
+      </c>
+      <c r="B461" t="s">
+        <v>909</v>
+      </c>
+      <c r="C461" t="s">
         <v>948</v>
-      </c>
-      <c r="B461" t="s">
-        <v>942</v>
-      </c>
-      <c r="C461" t="s">
-        <v>949</v>
       </c>
       <c r="D461" t="s">
         <v>18</v>
@@ -11371,10 +11395,10 @@
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
+        <v>949</v>
+      </c>
+      <c r="B462" t="s">
         <v>950</v>
-      </c>
-      <c r="B462" t="s">
-        <v>942</v>
       </c>
       <c r="C462" t="s">
         <v>951</v>
@@ -11391,13 +11415,13 @@
         <v>952</v>
       </c>
       <c r="B463" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C463" t="s">
         <v>953</v>
       </c>
       <c r="D463" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E463" t="s">
         <v>9</v>
@@ -11408,13 +11432,13 @@
         <v>954</v>
       </c>
       <c r="B464" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C464" t="s">
         <v>955</v>
       </c>
       <c r="D464" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E464" t="s">
         <v>9</v>
@@ -11425,7 +11449,7 @@
         <v>956</v>
       </c>
       <c r="B465" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C465" t="s">
         <v>957</v>
@@ -11442,13 +11466,13 @@
         <v>958</v>
       </c>
       <c r="B466" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C466" t="s">
         <v>959</v>
       </c>
       <c r="D466" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E466" t="s">
         <v>9</v>
@@ -11459,13 +11483,13 @@
         <v>960</v>
       </c>
       <c r="B467" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C467" t="s">
         <v>961</v>
       </c>
       <c r="D467" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E467" t="s">
         <v>9</v>
@@ -11476,7 +11500,7 @@
         <v>962</v>
       </c>
       <c r="B468" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C468" t="s">
         <v>963</v>
@@ -11493,7 +11517,7 @@
         <v>964</v>
       </c>
       <c r="B469" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C469" t="s">
         <v>965</v>
@@ -11510,13 +11534,13 @@
         <v>966</v>
       </c>
       <c r="B470" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C470" t="s">
         <v>967</v>
       </c>
       <c r="D470" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E470" t="s">
         <v>9</v>
@@ -11527,7 +11551,7 @@
         <v>968</v>
       </c>
       <c r="B471" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C471" t="s">
         <v>969</v>
@@ -11544,13 +11568,13 @@
         <v>970</v>
       </c>
       <c r="B472" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C472" t="s">
         <v>971</v>
       </c>
       <c r="D472" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E472" t="s">
         <v>9</v>
@@ -11561,7 +11585,7 @@
         <v>972</v>
       </c>
       <c r="B473" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C473" t="s">
         <v>973</v>
@@ -11578,7 +11602,7 @@
         <v>974</v>
       </c>
       <c r="B474" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C474" t="s">
         <v>975</v>
@@ -11595,13 +11619,13 @@
         <v>976</v>
       </c>
       <c r="B475" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C475" t="s">
         <v>977</v>
       </c>
       <c r="D475" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E475" t="s">
         <v>9</v>
@@ -11612,13 +11636,13 @@
         <v>978</v>
       </c>
       <c r="B476" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C476" t="s">
         <v>979</v>
       </c>
       <c r="D476" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E476" t="s">
         <v>9</v>
@@ -11629,7 +11653,7 @@
         <v>980</v>
       </c>
       <c r="B477" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C477" t="s">
         <v>981</v>
@@ -11646,13 +11670,13 @@
         <v>982</v>
       </c>
       <c r="B478" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C478" t="s">
         <v>983</v>
       </c>
       <c r="D478" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E478" t="s">
         <v>9</v>
@@ -11663,13 +11687,13 @@
         <v>984</v>
       </c>
       <c r="B479" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C479" t="s">
         <v>985</v>
       </c>
       <c r="D479" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E479" t="s">
         <v>9</v>
@@ -11680,7 +11704,7 @@
         <v>986</v>
       </c>
       <c r="B480" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C480" t="s">
         <v>987</v>
@@ -11697,7 +11721,7 @@
         <v>988</v>
       </c>
       <c r="B481" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C481" t="s">
         <v>989</v>
@@ -11714,13 +11738,13 @@
         <v>990</v>
       </c>
       <c r="B482" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C482" t="s">
         <v>991</v>
       </c>
       <c r="D482" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E482" t="s">
         <v>9</v>
@@ -11731,7 +11755,7 @@
         <v>992</v>
       </c>
       <c r="B483" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C483" t="s">
         <v>993</v>
@@ -11748,13 +11772,13 @@
         <v>994</v>
       </c>
       <c r="B484" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C484" t="s">
         <v>995</v>
       </c>
       <c r="D484" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E484" t="s">
         <v>9</v>
@@ -11765,7 +11789,7 @@
         <v>996</v>
       </c>
       <c r="B485" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C485" t="s">
         <v>997</v>
@@ -11782,7 +11806,7 @@
         <v>998</v>
       </c>
       <c r="B486" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C486" t="s">
         <v>999</v>
@@ -11799,13 +11823,13 @@
         <v>1000</v>
       </c>
       <c r="B487" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C487" t="s">
         <v>1001</v>
       </c>
       <c r="D487" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E487" t="s">
         <v>9</v>
@@ -11816,13 +11840,13 @@
         <v>1002</v>
       </c>
       <c r="B488" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C488" t="s">
         <v>1003</v>
       </c>
       <c r="D488" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E488" t="s">
         <v>9</v>
@@ -11833,7 +11857,7 @@
         <v>1004</v>
       </c>
       <c r="B489" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C489" t="s">
         <v>1005</v>
@@ -11850,13 +11874,13 @@
         <v>1006</v>
       </c>
       <c r="B490" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C490" t="s">
         <v>1007</v>
       </c>
       <c r="D490" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E490" t="s">
         <v>9</v>
@@ -11867,13 +11891,13 @@
         <v>1008</v>
       </c>
       <c r="B491" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C491" t="s">
         <v>1009</v>
       </c>
       <c r="D491" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E491" t="s">
         <v>9</v>
@@ -11884,7 +11908,7 @@
         <v>1010</v>
       </c>
       <c r="B492" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C492" t="s">
         <v>1011</v>
@@ -11901,7 +11925,7 @@
         <v>1012</v>
       </c>
       <c r="B493" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C493" t="s">
         <v>1013</v>
@@ -11918,13 +11942,13 @@
         <v>1014</v>
       </c>
       <c r="B494" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C494" t="s">
         <v>1015</v>
       </c>
       <c r="D494" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E494" t="s">
         <v>9</v>
@@ -11935,7 +11959,7 @@
         <v>1016</v>
       </c>
       <c r="B495" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C495" t="s">
         <v>1017</v>
@@ -11952,13 +11976,13 @@
         <v>1018</v>
       </c>
       <c r="B496" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C496" t="s">
         <v>1019</v>
       </c>
       <c r="D496" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E496" t="s">
         <v>9</v>
@@ -11969,7 +11993,7 @@
         <v>1020</v>
       </c>
       <c r="B497" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C497" t="s">
         <v>1021</v>
@@ -11986,7 +12010,7 @@
         <v>1022</v>
       </c>
       <c r="B498" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C498" t="s">
         <v>1023</v>
@@ -12003,13 +12027,13 @@
         <v>1024</v>
       </c>
       <c r="B499" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C499" t="s">
         <v>1025</v>
       </c>
       <c r="D499" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E499" t="s">
         <v>9</v>
@@ -12020,13 +12044,13 @@
         <v>1026</v>
       </c>
       <c r="B500" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C500" t="s">
         <v>1027</v>
       </c>
       <c r="D500" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E500" t="s">
         <v>9</v>
@@ -12037,7 +12061,7 @@
         <v>1028</v>
       </c>
       <c r="B501" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C501" t="s">
         <v>1029</v>
@@ -12054,13 +12078,13 @@
         <v>1030</v>
       </c>
       <c r="B502" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C502" t="s">
         <v>1031</v>
       </c>
       <c r="D502" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E502" t="s">
         <v>9</v>
@@ -12071,13 +12095,13 @@
         <v>1032</v>
       </c>
       <c r="B503" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C503" t="s">
         <v>1033</v>
       </c>
       <c r="D503" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E503" t="s">
         <v>9</v>
@@ -12088,7 +12112,7 @@
         <v>1034</v>
       </c>
       <c r="B504" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C504" t="s">
         <v>1035</v>
@@ -12105,7 +12129,7 @@
         <v>1036</v>
       </c>
       <c r="B505" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C505" t="s">
         <v>1037</v>
@@ -12122,13 +12146,13 @@
         <v>1038</v>
       </c>
       <c r="B506" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C506" t="s">
         <v>1039</v>
       </c>
       <c r="D506" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E506" t="s">
         <v>9</v>
@@ -12139,7 +12163,7 @@
         <v>1040</v>
       </c>
       <c r="B507" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="C507" t="s">
         <v>1041</v>
@@ -12148,6 +12172,74 @@
         <v>12</v>
       </c>
       <c r="E507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="508" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B508" t="s">
+        <v>950</v>
+      </c>
+      <c r="C508" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D508" t="s">
+        <v>8</v>
+      </c>
+      <c r="E508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="509" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B509" t="s">
+        <v>950</v>
+      </c>
+      <c r="C509" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D509" t="s">
+        <v>18</v>
+      </c>
+      <c r="E509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="510" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B510" t="s">
+        <v>950</v>
+      </c>
+      <c r="C510" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D510" t="s">
+        <v>8</v>
+      </c>
+      <c r="E510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="511" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B511" t="s">
+        <v>950</v>
+      </c>
+      <c r="C511" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D511" t="s">
+        <v>12</v>
+      </c>
+      <c r="E511" t="s">
         <v>9</v>
       </c>
     </row>
